--- a/research/traditional_assets/database/data/belgium/belgium_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_software_entertainment.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.09601449275362318</v>
+        <v>-0.05705329153605017</v>
       </c>
       <c r="H2">
-        <v>-0.1539855072463768</v>
+        <v>-0.1605015673981191</v>
       </c>
       <c r="I2">
-        <v>-0.1576086956521739</v>
+        <v>-0.2075235109717868</v>
       </c>
       <c r="J2">
-        <v>-0.1576086956521739</v>
+        <v>-0.2075235109717868</v>
       </c>
       <c r="K2">
-        <v>-5.58</v>
+        <v>-9.02</v>
       </c>
       <c r="L2">
-        <v>-0.2021739130434783</v>
+        <v>-0.2827586206896552</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.33</v>
+        <v>3.28</v>
       </c>
       <c r="V2">
-        <v>0.1094455852156057</v>
+        <v>0.4004884004884005</v>
       </c>
       <c r="W2">
-        <v>-0.3049180327868852</v>
+        <v>-0.3822033898305084</v>
       </c>
       <c r="X2">
-        <v>0.09070971131459815</v>
+        <v>0.3646318223043165</v>
       </c>
       <c r="Y2">
-        <v>-0.3956277441014834</v>
+        <v>-0.746835212134825</v>
       </c>
       <c r="Z2">
-        <v>0.997578342429609</v>
+        <v>1.237873496313543</v>
       </c>
       <c r="AA2">
-        <v>-0.1572270213611884</v>
+        <v>-0.2568878540939076</v>
       </c>
       <c r="AB2">
-        <v>0.07161978471921072</v>
+        <v>0.1297530215062762</v>
       </c>
       <c r="AC2">
-        <v>-0.2288468060803991</v>
+        <v>-0.3866408756001838</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AG2">
-        <v>13.17</v>
+        <v>20.72</v>
       </c>
       <c r="AH2">
-        <v>0.275297619047619</v>
+        <v>0.7455731593662629</v>
       </c>
       <c r="AI2">
-        <v>0.4404761904761905</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="AJ2">
-        <v>0.2128656861160498</v>
+        <v>0.7167070217917676</v>
       </c>
       <c r="AK2">
-        <v>0.3591491682574312</v>
+        <v>0.6430788330229671</v>
       </c>
       <c r="AL2">
-        <v>1.34</v>
+        <v>3.24</v>
       </c>
       <c r="AM2">
-        <v>1.338</v>
+        <v>3.24</v>
       </c>
       <c r="AN2">
-        <v>-3.927813163481953</v>
+        <v>-2.952029520295202</v>
       </c>
       <c r="AO2">
-        <v>-3.246268656716417</v>
+        <v>-2.04320987654321</v>
       </c>
       <c r="AP2">
-        <v>-2.796178343949045</v>
+        <v>-2.548585485854858</v>
       </c>
       <c r="AQ2">
-        <v>-3.251121076233183</v>
+        <v>-2.04320987654321</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AudioValley SA (ENXTPA:ALAVY)</t>
+          <t>Targetspot (ENXTPA:ALTGS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.09601449275362318</v>
+        <v>-0.05705329153605017</v>
       </c>
       <c r="H3">
-        <v>-0.1539855072463768</v>
+        <v>-0.1605015673981191</v>
       </c>
       <c r="I3">
-        <v>-0.1576086956521739</v>
+        <v>-0.2075235109717868</v>
       </c>
       <c r="J3">
-        <v>-0.1576086956521739</v>
+        <v>-0.2075235109717868</v>
       </c>
       <c r="K3">
-        <v>-5.58</v>
+        <v>-9.02</v>
       </c>
       <c r="L3">
-        <v>-0.2021739130434783</v>
+        <v>-0.2827586206896552</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.33</v>
+        <v>3.28</v>
       </c>
       <c r="V3">
-        <v>0.1094455852156057</v>
+        <v>0.4004884004884005</v>
       </c>
       <c r="W3">
-        <v>-0.3049180327868852</v>
+        <v>-0.3822033898305084</v>
       </c>
       <c r="X3">
-        <v>0.09070971131459815</v>
+        <v>0.3646318223043165</v>
       </c>
       <c r="Y3">
-        <v>-0.3956277441014834</v>
+        <v>-0.746835212134825</v>
       </c>
       <c r="Z3">
-        <v>0.997578342429609</v>
+        <v>1.237873496313543</v>
       </c>
       <c r="AA3">
-        <v>-0.1572270213611884</v>
+        <v>-0.2568878540939076</v>
       </c>
       <c r="AB3">
-        <v>0.07161978471921072</v>
+        <v>0.1297530215062762</v>
       </c>
       <c r="AC3">
-        <v>-0.2288468060803991</v>
+        <v>-0.3866408756001838</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AG3">
-        <v>13.17</v>
+        <v>20.72</v>
       </c>
       <c r="AH3">
-        <v>0.275297619047619</v>
+        <v>0.7455731593662629</v>
       </c>
       <c r="AI3">
-        <v>0.4404761904761905</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="AJ3">
-        <v>0.2128656861160498</v>
+        <v>0.7167070217917676</v>
       </c>
       <c r="AK3">
-        <v>0.3591491682574312</v>
+        <v>0.6430788330229671</v>
       </c>
       <c r="AL3">
-        <v>1.34</v>
+        <v>3.24</v>
       </c>
       <c r="AM3">
-        <v>1.338</v>
+        <v>3.24</v>
       </c>
       <c r="AN3">
-        <v>-3.927813163481953</v>
+        <v>-2.952029520295202</v>
       </c>
       <c r="AO3">
-        <v>-3.246268656716417</v>
+        <v>-2.04320987654321</v>
       </c>
       <c r="AP3">
-        <v>-2.796178343949045</v>
+        <v>-2.548585485854858</v>
       </c>
       <c r="AQ3">
-        <v>-3.251121076233183</v>
+        <v>-2.04320987654321</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_software_entertainment.xlsx
@@ -587,32 +587,17 @@
           <t>Software (Entertainment)</t>
         </is>
       </c>
-      <c r="G2">
-        <v>-0.05705329153605017</v>
-      </c>
-      <c r="H2">
-        <v>-0.1605015673981191</v>
-      </c>
-      <c r="I2">
-        <v>-0.2075235109717868</v>
-      </c>
-      <c r="J2">
-        <v>-0.2075235109717868</v>
-      </c>
       <c r="K2">
-        <v>-9.02</v>
-      </c>
-      <c r="L2">
-        <v>-0.2827586206896552</v>
+        <v>-13.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01032064128256513</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.007629629629629629</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +609,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
+        <v>0.103</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>0.294</v>
+      </c>
+      <c r="V2">
+        <v>0.02945891783567134</v>
+      </c>
+      <c r="W2">
+        <v>-1.184210526315789</v>
+      </c>
+      <c r="X2">
+        <v>0.2216413876624297</v>
+      </c>
+      <c r="Y2">
+        <v>-1.405851913978219</v>
+      </c>
+      <c r="Z2">
         <v>0</v>
       </c>
-      <c r="U2">
-        <v>3.28</v>
-      </c>
-      <c r="V2">
-        <v>0.4004884004884005</v>
-      </c>
-      <c r="W2">
-        <v>-0.3822033898305084</v>
-      </c>
-      <c r="X2">
-        <v>0.3646318223043165</v>
-      </c>
-      <c r="Y2">
-        <v>-0.746835212134825</v>
-      </c>
-      <c r="Z2">
-        <v>1.237873496313543</v>
-      </c>
       <c r="AA2">
-        <v>-0.2568878540939076</v>
+        <v>-0.6634016028495103</v>
       </c>
       <c r="AB2">
-        <v>0.1297530215062762</v>
+        <v>0.1397396156522919</v>
       </c>
       <c r="AC2">
-        <v>-0.3866408756001838</v>
+        <v>-0.8031412185018023</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AG2">
-        <v>20.72</v>
+        <v>19.206</v>
       </c>
       <c r="AH2">
-        <v>0.7455731593662629</v>
+        <v>0.6614654002713705</v>
       </c>
       <c r="AI2">
-        <v>0.676056338028169</v>
+        <v>0.937950937950938</v>
       </c>
       <c r="AJ2">
-        <v>0.7167070217917676</v>
+        <v>0.658055231960529</v>
       </c>
       <c r="AK2">
-        <v>0.6430788330229671</v>
+        <v>0.9370608899297425</v>
       </c>
       <c r="AL2">
-        <v>3.24</v>
+        <v>1.4</v>
       </c>
       <c r="AM2">
-        <v>3.24</v>
+        <v>1.267</v>
       </c>
       <c r="AN2">
-        <v>-2.952029520295202</v>
+        <v>-1.444444444444444</v>
       </c>
       <c r="AO2">
-        <v>-2.04320987654321</v>
+        <v>-10.64285714285714</v>
       </c>
       <c r="AP2">
-        <v>-2.548585485854858</v>
+        <v>-1.422666666666667</v>
       </c>
       <c r="AQ2">
-        <v>-2.04320987654321</v>
+        <v>-11.76006314127861</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +692,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Targetspot (ENXTPA:ALTGS)</t>
+          <t>Llama Group SA (ENXTPA:ALLAM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,32 +700,17 @@
           <t>Software (Entertainment)</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-0.05705329153605017</v>
-      </c>
-      <c r="H3">
-        <v>-0.1605015673981191</v>
-      </c>
-      <c r="I3">
-        <v>-0.2075235109717868</v>
-      </c>
-      <c r="J3">
-        <v>-0.2075235109717868</v>
-      </c>
       <c r="K3">
-        <v>-9.02</v>
-      </c>
-      <c r="L3">
-        <v>-0.2827586206896552</v>
+        <v>-13.5</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.103</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01032064128256513</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.007629629629629629</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +722,79 @@
         <v>0</v>
       </c>
       <c r="S3">
+        <v>0.103</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>0.294</v>
+      </c>
+      <c r="V3">
+        <v>0.02945891783567134</v>
+      </c>
+      <c r="W3">
+        <v>-1.184210526315789</v>
+      </c>
+      <c r="X3">
+        <v>0.2216413876624297</v>
+      </c>
+      <c r="Y3">
+        <v>-1.405851913978219</v>
+      </c>
+      <c r="Z3">
         <v>0</v>
       </c>
-      <c r="U3">
-        <v>3.28</v>
-      </c>
-      <c r="V3">
-        <v>0.4004884004884005</v>
-      </c>
-      <c r="W3">
-        <v>-0.3822033898305084</v>
-      </c>
-      <c r="X3">
-        <v>0.3646318223043165</v>
-      </c>
-      <c r="Y3">
-        <v>-0.746835212134825</v>
-      </c>
-      <c r="Z3">
-        <v>1.237873496313543</v>
-      </c>
       <c r="AA3">
-        <v>-0.2568878540939076</v>
+        <v>-0.6634016028495103</v>
       </c>
       <c r="AB3">
-        <v>0.1297530215062762</v>
+        <v>0.1397396156522919</v>
       </c>
       <c r="AC3">
-        <v>-0.3866408756001838</v>
+        <v>-0.8031412185018023</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>20.72</v>
+        <v>19.206</v>
       </c>
       <c r="AH3">
-        <v>0.7455731593662629</v>
+        <v>0.6614654002713705</v>
       </c>
       <c r="AI3">
-        <v>0.676056338028169</v>
+        <v>0.937950937950938</v>
       </c>
       <c r="AJ3">
-        <v>0.7167070217917676</v>
+        <v>0.658055231960529</v>
       </c>
       <c r="AK3">
-        <v>0.6430788330229671</v>
+        <v>0.9370608899297425</v>
       </c>
       <c r="AL3">
-        <v>3.24</v>
+        <v>1.4</v>
       </c>
       <c r="AM3">
-        <v>3.24</v>
+        <v>1.267</v>
       </c>
       <c r="AN3">
-        <v>-2.952029520295202</v>
+        <v>-1.444444444444444</v>
       </c>
       <c r="AO3">
-        <v>-2.04320987654321</v>
+        <v>-10.64285714285714</v>
       </c>
       <c r="AP3">
-        <v>-2.548585485854858</v>
+        <v>-1.422666666666667</v>
       </c>
       <c r="AQ3">
-        <v>-2.04320987654321</v>
+        <v>-11.76006314127861</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_software_entertainment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1152725673289365</v>
+        <v>0.1150181359106141</v>
       </c>
       <c r="C2">
-        <v>25.17997917995045</v>
+        <v>24.99384403693767</v>
       </c>
       <c r="D2">
-        <v>24.83897917995045</v>
+        <v>24.87984403693767</v>
       </c>
       <c r="E2">
-        <v>-12.9</v>
+        <v>-12.673</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="G2">
         <v>0.341</v>
@@ -1439,28 +1439,28 @@
         <v>2.29</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0114181</v>
       </c>
       <c r="N2">
-        <v>2.29</v>
+        <v>2.2785819</v>
       </c>
       <c r="O2">
-        <v>0.5725</v>
+        <v>0.569645475</v>
       </c>
       <c r="P2">
-        <v>1.7175</v>
+        <v>1.708936425</v>
       </c>
       <c r="Q2">
-        <v>4.0475</v>
+        <v>4.038936425</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1152725673289365</v>
+        <v>0.115798874657186</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.364408355905439</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>200.558761965651</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1150181359106141</v>
+        <v>0.1147637044922918</v>
       </c>
       <c r="C3">
-        <v>24.99384403693767</v>
+        <v>24.80784357646687</v>
       </c>
       <c r="D3">
-        <v>24.87984403693767</v>
+        <v>24.92084357646686</v>
       </c>
       <c r="E3">
-        <v>-12.673</v>
+        <v>-12.446</v>
       </c>
       <c r="F3">
-        <v>0.227</v>
+        <v>0.4540000000000001</v>
       </c>
       <c r="G3">
         <v>0.341</v>
@@ -1521,28 +1521,28 @@
         <v>2.29</v>
       </c>
       <c r="M3">
-        <v>0.0114181</v>
+        <v>0.0228362</v>
       </c>
       <c r="N3">
-        <v>2.2785819</v>
+        <v>2.2671638</v>
       </c>
       <c r="O3">
-        <v>0.569645475</v>
+        <v>0.56679095</v>
       </c>
       <c r="P3">
-        <v>1.708936425</v>
+        <v>1.70037285</v>
       </c>
       <c r="Q3">
-        <v>4.038936425</v>
+        <v>4.03037285</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.115798874657186</v>
+        <v>0.1163359229513181</v>
       </c>
       <c r="T3">
-        <v>1.364408355905439</v>
+        <v>1.374876426765539</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>200.558761965651</v>
+        <v>100.2793809828255</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1147637044922918</v>
+        <v>0.1145092730739694</v>
       </c>
       <c r="C4">
-        <v>24.80784357646687</v>
+        <v>24.62197846546788</v>
       </c>
       <c r="D4">
-        <v>24.92084357646686</v>
+        <v>24.96197846546788</v>
       </c>
       <c r="E4">
-        <v>-12.446</v>
+        <v>-12.219</v>
       </c>
       <c r="F4">
-        <v>0.4540000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="G4">
         <v>0.341</v>
@@ -1603,28 +1603,28 @@
         <v>2.29</v>
       </c>
       <c r="M4">
-        <v>0.0228362</v>
+        <v>0.0342543</v>
       </c>
       <c r="N4">
-        <v>2.2671638</v>
+        <v>2.2557457</v>
       </c>
       <c r="O4">
-        <v>0.56679095</v>
+        <v>0.563936425</v>
       </c>
       <c r="P4">
-        <v>1.70037285</v>
+        <v>1.691809275</v>
       </c>
       <c r="Q4">
-        <v>4.03037285</v>
+        <v>4.021809275</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1163359229513181</v>
+        <v>0.116884044406154</v>
       </c>
       <c r="T4">
-        <v>1.374876426765539</v>
+        <v>1.385560334138218</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.2793809828255</v>
+        <v>66.85292065521701</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1145092730739694</v>
+        <v>0.1142548416556471</v>
       </c>
       <c r="C5">
-        <v>24.62197846546788</v>
+        <v>24.43624937528122</v>
       </c>
       <c r="D5">
-        <v>24.96197846546788</v>
+        <v>25.00324937528122</v>
       </c>
       <c r="E5">
-        <v>-12.219</v>
+        <v>-11.992</v>
       </c>
       <c r="F5">
-        <v>0.681</v>
+        <v>0.9080000000000001</v>
       </c>
       <c r="G5">
         <v>0.341</v>
@@ -1685,28 +1685,28 @@
         <v>2.29</v>
       </c>
       <c r="M5">
-        <v>0.0342543</v>
+        <v>0.0456724</v>
       </c>
       <c r="N5">
-        <v>2.2557457</v>
+        <v>2.2443276</v>
       </c>
       <c r="O5">
-        <v>0.563936425</v>
+        <v>0.5610819</v>
       </c>
       <c r="P5">
-        <v>1.691809275</v>
+        <v>1.6832457</v>
       </c>
       <c r="Q5">
-        <v>4.021809275</v>
+        <v>4.013245700000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.116884044406154</v>
+        <v>0.1174435850579657</v>
       </c>
       <c r="T5">
-        <v>1.385560334138218</v>
+        <v>1.396466822914495</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.85292065521701</v>
+        <v>50.13969049141276</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1142548416556471</v>
+        <v>0.1140004102373248</v>
       </c>
       <c r="C6">
-        <v>24.43624937528122</v>
+        <v>24.25065698169461</v>
       </c>
       <c r="D6">
-        <v>25.00324937528122</v>
+        <v>25.04465698169461</v>
       </c>
       <c r="E6">
-        <v>-11.992</v>
+        <v>-11.765</v>
       </c>
       <c r="F6">
-        <v>0.9080000000000001</v>
+        <v>1.135</v>
       </c>
       <c r="G6">
         <v>0.341</v>
@@ -1767,28 +1767,28 @@
         <v>2.29</v>
       </c>
       <c r="M6">
-        <v>0.0456724</v>
+        <v>0.05709050000000001</v>
       </c>
       <c r="N6">
-        <v>2.2443276</v>
+        <v>2.2329095</v>
       </c>
       <c r="O6">
-        <v>0.5610819</v>
+        <v>0.558227375</v>
       </c>
       <c r="P6">
-        <v>1.6832457</v>
+        <v>1.674682125</v>
       </c>
       <c r="Q6">
-        <v>4.013245700000001</v>
+        <v>4.004682125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1174435850579657</v>
+        <v>0.1180149055129734</v>
       </c>
       <c r="T6">
-        <v>1.396466822914495</v>
+        <v>1.407602921980799</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.13969049141276</v>
+        <v>40.1117523931302</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1140004102373248</v>
+        <v>0.1137459788190024</v>
       </c>
       <c r="C7">
-        <v>24.25065698169461</v>
+        <v>24.06520196497985</v>
       </c>
       <c r="D7">
-        <v>25.04465698169461</v>
+        <v>25.08620196497985</v>
       </c>
       <c r="E7">
-        <v>-11.765</v>
+        <v>-11.538</v>
       </c>
       <c r="F7">
-        <v>1.135</v>
+        <v>1.362</v>
       </c>
       <c r="G7">
         <v>0.341</v>
@@ -1849,28 +1849,28 @@
         <v>2.29</v>
       </c>
       <c r="M7">
-        <v>0.05709050000000001</v>
+        <v>0.06850860000000002</v>
       </c>
       <c r="N7">
-        <v>2.2329095</v>
+        <v>2.2214914</v>
       </c>
       <c r="O7">
-        <v>0.558227375</v>
+        <v>0.55537285</v>
       </c>
       <c r="P7">
-        <v>1.674682125</v>
+        <v>1.66611855</v>
       </c>
       <c r="Q7">
-        <v>4.004682125</v>
+        <v>3.99611855</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1180149055129734</v>
+        <v>0.118598381722343</v>
       </c>
       <c r="T7">
-        <v>1.407602921980799</v>
+        <v>1.418975959325109</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.1117523931302</v>
+        <v>33.4264603276085</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1137459788190024</v>
+        <v>0.1134915474006801</v>
       </c>
       <c r="C8">
-        <v>24.06520196497985</v>
+        <v>23.87988500993008</v>
       </c>
       <c r="D8">
-        <v>25.08620196497985</v>
+        <v>25.12788500993008</v>
       </c>
       <c r="E8">
-        <v>-11.538</v>
+        <v>-11.311</v>
       </c>
       <c r="F8">
-        <v>1.362</v>
+        <v>1.589</v>
       </c>
       <c r="G8">
         <v>0.341</v>
@@ -1931,28 +1931,28 @@
         <v>2.29</v>
       </c>
       <c r="M8">
-        <v>0.0685086</v>
+        <v>0.07992669999999999</v>
       </c>
       <c r="N8">
-        <v>2.2214914</v>
+        <v>2.2100733</v>
       </c>
       <c r="O8">
-        <v>0.55537285</v>
+        <v>0.552518325</v>
       </c>
       <c r="P8">
-        <v>1.66611855</v>
+        <v>1.657554975</v>
       </c>
       <c r="Q8">
-        <v>3.99611855</v>
+        <v>3.987554975</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.118598381722343</v>
+        <v>0.1191944058071829</v>
       </c>
       <c r="T8">
-        <v>1.418975959325109</v>
+        <v>1.430593578117684</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.4264603276085</v>
+        <v>28.65125170937872</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.11349154740068</v>
+        <v>0.1132371159823577</v>
       </c>
       <c r="C9">
-        <v>23.87988500993008</v>
+        <v>23.69470680589739</v>
       </c>
       <c r="D9">
-        <v>25.12788500993008</v>
+        <v>25.16970680589739</v>
       </c>
       <c r="E9">
-        <v>-11.311</v>
+        <v>-11.084</v>
       </c>
       <c r="F9">
-        <v>1.589</v>
+        <v>1.816</v>
       </c>
       <c r="G9">
         <v>0.341</v>
@@ -2013,28 +2013,28 @@
         <v>2.29</v>
       </c>
       <c r="M9">
-        <v>0.07992670000000002</v>
+        <v>0.0913448</v>
       </c>
       <c r="N9">
-        <v>2.2100733</v>
+        <v>2.1986552</v>
       </c>
       <c r="O9">
-        <v>0.552518325</v>
+        <v>0.5496638</v>
       </c>
       <c r="P9">
-        <v>1.657554975</v>
+        <v>1.6489914</v>
       </c>
       <c r="Q9">
-        <v>3.987554975</v>
+        <v>3.9789914</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1191944058071829</v>
+        <v>0.1198033869373454</v>
       </c>
       <c r="T9">
-        <v>1.430593578117684</v>
+        <v>1.442463753840533</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.65125170937871</v>
+        <v>25.06984524570638</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1132371159823577</v>
+        <v>0.1129826845640354</v>
       </c>
       <c r="C10">
-        <v>23.69470680589739</v>
+        <v>23.50966804683086</v>
       </c>
       <c r="D10">
-        <v>25.16970680589739</v>
+        <v>25.21166804683086</v>
       </c>
       <c r="E10">
-        <v>-11.084</v>
+        <v>-10.857</v>
       </c>
       <c r="F10">
-        <v>1.816</v>
+        <v>2.043</v>
       </c>
       <c r="G10">
         <v>0.341</v>
@@ -2095,28 +2095,28 @@
         <v>2.29</v>
       </c>
       <c r="M10">
-        <v>0.0913448</v>
+        <v>0.1027629</v>
       </c>
       <c r="N10">
-        <v>2.1986552</v>
+        <v>2.1872371</v>
       </c>
       <c r="O10">
-        <v>0.5496638</v>
+        <v>0.546809275</v>
       </c>
       <c r="P10">
-        <v>1.6489914</v>
+        <v>1.640427825</v>
       </c>
       <c r="Q10">
-        <v>3.9789914</v>
+        <v>3.970427825</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1198033869373454</v>
+        <v>0.1204257522681708</v>
       </c>
       <c r="T10">
-        <v>1.442463753840533</v>
+        <v>1.454594812546301</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.06984524570638</v>
+        <v>22.28430688507234</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1129826845640354</v>
+        <v>0.1127282531457131</v>
       </c>
       <c r="C11">
-        <v>23.50966804683086</v>
+        <v>23.3247694313149</v>
       </c>
       <c r="D11">
-        <v>25.21166804683086</v>
+        <v>25.2537694313149</v>
       </c>
       <c r="E11">
-        <v>-10.857</v>
+        <v>-10.63</v>
       </c>
       <c r="F11">
-        <v>2.043</v>
+        <v>2.27</v>
       </c>
       <c r="G11">
         <v>0.341</v>
@@ -2177,28 +2177,28 @@
         <v>2.29</v>
       </c>
       <c r="M11">
-        <v>0.1027629</v>
+        <v>0.114181</v>
       </c>
       <c r="N11">
-        <v>2.1872371</v>
+        <v>2.175819</v>
       </c>
       <c r="O11">
-        <v>0.546809275</v>
+        <v>0.54395475</v>
       </c>
       <c r="P11">
-        <v>1.640427825</v>
+        <v>1.63186425</v>
       </c>
       <c r="Q11">
-        <v>3.970427825</v>
+        <v>3.96186425</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1204257522681708</v>
+        <v>0.1210619479396812</v>
       </c>
       <c r="T11">
-        <v>1.454594812546301</v>
+        <v>1.466995450334419</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.28430688507234</v>
+        <v>20.05587619656511</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1127282531457131</v>
+        <v>0.1124738217273907</v>
       </c>
       <c r="C12">
-        <v>23.3247694313149</v>
+        <v>23.14001166260805</v>
       </c>
       <c r="D12">
-        <v>25.2537694313149</v>
+        <v>25.29601166260805</v>
       </c>
       <c r="E12">
-        <v>-10.63</v>
+        <v>-10.403</v>
       </c>
       <c r="F12">
-        <v>2.27</v>
+        <v>2.497</v>
       </c>
       <c r="G12">
         <v>0.341</v>
@@ -2259,28 +2259,28 @@
         <v>2.29</v>
       </c>
       <c r="M12">
-        <v>0.114181</v>
+        <v>0.1255991</v>
       </c>
       <c r="N12">
-        <v>2.175819</v>
+        <v>2.1644009</v>
       </c>
       <c r="O12">
-        <v>0.54395475</v>
+        <v>0.541100225</v>
       </c>
       <c r="P12">
-        <v>1.63186425</v>
+        <v>1.623300675</v>
       </c>
       <c r="Q12">
-        <v>3.96186425</v>
+        <v>3.953300675</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1210619479396812</v>
+        <v>0.1217124401431356</v>
       </c>
       <c r="T12">
-        <v>1.466995450334419</v>
+        <v>1.479674754140248</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.0558761965651</v>
+        <v>18.23261472415009</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1124738217273907</v>
+        <v>0.1122193903090684</v>
       </c>
       <c r="C13">
-        <v>23.14001166260805</v>
+        <v>22.9553954486821</v>
       </c>
       <c r="D13">
-        <v>25.29601166260805</v>
+        <v>25.3383954486821</v>
       </c>
       <c r="E13">
-        <v>-10.403</v>
+        <v>-10.176</v>
       </c>
       <c r="F13">
-        <v>2.497</v>
+        <v>2.724</v>
       </c>
       <c r="G13">
         <v>0.341</v>
@@ -2341,28 +2341,28 @@
         <v>2.29</v>
       </c>
       <c r="M13">
-        <v>0.1255991</v>
+        <v>0.1370172</v>
       </c>
       <c r="N13">
-        <v>2.1644009</v>
+        <v>2.1529828</v>
       </c>
       <c r="O13">
-        <v>0.541100225</v>
+        <v>0.5382457</v>
       </c>
       <c r="P13">
-        <v>1.623300675</v>
+        <v>1.6147371</v>
       </c>
       <c r="Q13">
-        <v>3.953300675</v>
+        <v>3.9447371</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1217124401431356</v>
+        <v>0.122377716260305</v>
       </c>
       <c r="T13">
-        <v>1.479674754140248</v>
+        <v>1.492642223941664</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.23261472415009</v>
+        <v>16.71323016380425</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1122193903090684</v>
+        <v>0.111964958890746</v>
       </c>
       <c r="C14">
-        <v>22.9553954486821</v>
+        <v>22.77092150226171</v>
       </c>
       <c r="D14">
-        <v>25.3383954486821</v>
+        <v>25.38092150226171</v>
       </c>
       <c r="E14">
-        <v>-10.176</v>
+        <v>-9.949</v>
       </c>
       <c r="F14">
-        <v>2.724</v>
+        <v>2.951000000000001</v>
       </c>
       <c r="G14">
         <v>0.341</v>
@@ -2423,28 +2423,28 @@
         <v>2.29</v>
       </c>
       <c r="M14">
-        <v>0.1370172</v>
+        <v>0.1484353</v>
       </c>
       <c r="N14">
-        <v>2.1529828</v>
+        <v>2.1415647</v>
       </c>
       <c r="O14">
-        <v>0.5382457</v>
+        <v>0.535391175</v>
       </c>
       <c r="P14">
-        <v>1.6147371</v>
+        <v>1.606173525</v>
       </c>
       <c r="Q14">
-        <v>3.9447371</v>
+        <v>3.936173525</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.122377716260305</v>
+        <v>0.1230582860813173</v>
       </c>
       <c r="T14">
-        <v>1.492642223941664</v>
+        <v>1.505907796497136</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.71323016380425</v>
+        <v>15.42759707428085</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.111964958890746</v>
+        <v>0.1117105274724237</v>
       </c>
       <c r="C15">
-        <v>22.77092150226171</v>
+        <v>22.58659054086426</v>
       </c>
       <c r="D15">
-        <v>25.38092150226171</v>
+        <v>25.42359054086426</v>
       </c>
       <c r="E15">
-        <v>-9.949</v>
+        <v>-9.722</v>
       </c>
       <c r="F15">
-        <v>2.951000000000001</v>
+        <v>3.178000000000001</v>
       </c>
       <c r="G15">
         <v>0.341</v>
@@ -2505,28 +2505,28 @@
         <v>2.29</v>
       </c>
       <c r="M15">
-        <v>0.1484353</v>
+        <v>0.1598534</v>
       </c>
       <c r="N15">
-        <v>2.1415647</v>
+        <v>2.1301466</v>
       </c>
       <c r="O15">
-        <v>0.535391175</v>
+        <v>0.5325366499999999</v>
       </c>
       <c r="P15">
-        <v>1.606173525</v>
+        <v>1.59760995</v>
       </c>
       <c r="Q15">
-        <v>3.936173525</v>
+        <v>3.92760995</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1230582860813173</v>
+        <v>0.1237546831074694</v>
       </c>
       <c r="T15">
-        <v>1.505907796497136</v>
+        <v>1.519481870739944</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.42759707428085</v>
+        <v>14.32562585468935</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1117105274724237</v>
+        <v>0.1114560960541014</v>
       </c>
       <c r="C16">
-        <v>22.58659054086426</v>
+        <v>22.40240328684031</v>
       </c>
       <c r="D16">
-        <v>25.42359054086426</v>
+        <v>25.46640328684031</v>
       </c>
       <c r="E16">
-        <v>-9.722</v>
+        <v>-9.494999999999999</v>
       </c>
       <c r="F16">
-        <v>3.178000000000001</v>
+        <v>3.405000000000001</v>
       </c>
       <c r="G16">
         <v>0.341</v>
@@ -2587,28 +2587,28 @@
         <v>2.29</v>
       </c>
       <c r="M16">
-        <v>0.1598534</v>
+        <v>0.1712715</v>
       </c>
       <c r="N16">
-        <v>2.1301466</v>
+        <v>2.1187285</v>
       </c>
       <c r="O16">
-        <v>0.5325366499999999</v>
+        <v>0.529682125</v>
       </c>
       <c r="P16">
-        <v>1.59760995</v>
+        <v>1.589046375</v>
       </c>
       <c r="Q16">
-        <v>3.92760995</v>
+        <v>3.919046375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1237546831074694</v>
+        <v>0.1244674659460016</v>
       </c>
       <c r="T16">
-        <v>1.519481870739944</v>
+        <v>1.533375334964936</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.32562585468935</v>
+        <v>13.3705841310434</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1114560960541014</v>
+        <v>0.111381664635779</v>
       </c>
       <c r="C17">
-        <v>22.40240328684031</v>
+        <v>22.18795501041963</v>
       </c>
       <c r="D17">
-        <v>25.46640328684031</v>
+        <v>25.47895501041963</v>
       </c>
       <c r="E17">
-        <v>-9.495000000000001</v>
+        <v>-9.268000000000001</v>
       </c>
       <c r="F17">
-        <v>3.405</v>
+        <v>3.632000000000001</v>
       </c>
       <c r="G17">
         <v>0.341</v>
@@ -2669,45 +2669,45 @@
         <v>2.29</v>
       </c>
       <c r="M17">
-        <v>0.1712715</v>
+        <v>0.1881376</v>
       </c>
       <c r="N17">
-        <v>2.1187285</v>
+        <v>2.1018624</v>
       </c>
       <c r="O17">
-        <v>0.529682125</v>
+        <v>0.5254656</v>
       </c>
       <c r="P17">
-        <v>1.589046375</v>
+        <v>1.5763968</v>
       </c>
       <c r="Q17">
-        <v>3.919046375</v>
+        <v>3.9063968</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1244674659460016</v>
+        <v>0.1251972198044988</v>
       </c>
       <c r="T17">
-        <v>1.533375334964936</v>
+        <v>1.54759959595719</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.3705841310434</v>
+        <v>12.17194223802153</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.111381664635779</v>
+        <v>0.1111384832174567</v>
       </c>
       <c r="C18">
-        <v>22.18795501041963</v>
+        <v>22.00205023625712</v>
       </c>
       <c r="D18">
-        <v>25.47895501041963</v>
+        <v>25.52005023625712</v>
       </c>
       <c r="E18">
-        <v>-9.268000000000001</v>
+        <v>-9.041</v>
       </c>
       <c r="F18">
-        <v>3.632000000000001</v>
+        <v>3.859000000000001</v>
       </c>
       <c r="G18">
         <v>0.341</v>
@@ -2751,28 +2751,28 @@
         <v>2.29</v>
       </c>
       <c r="M18">
-        <v>0.1881376</v>
+        <v>0.1998962000000001</v>
       </c>
       <c r="N18">
-        <v>2.1018624</v>
+        <v>2.0901038</v>
       </c>
       <c r="O18">
-        <v>0.5254656</v>
+        <v>0.52252595</v>
       </c>
       <c r="P18">
-        <v>1.5763968</v>
+        <v>1.56757785</v>
       </c>
       <c r="Q18">
-        <v>3.9063968</v>
+        <v>3.89757785</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1251972198044988</v>
+        <v>0.1259445580933213</v>
       </c>
       <c r="T18">
-        <v>1.54759959595719</v>
+        <v>1.562166610226365</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.17194223802153</v>
+        <v>11.45594563578497</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1111384832174567</v>
+        <v>0.1108953017991343</v>
       </c>
       <c r="C19">
-        <v>22.00205023625712</v>
+        <v>21.8162782419433</v>
       </c>
       <c r="D19">
-        <v>25.52005023625712</v>
+        <v>25.5612782419433</v>
       </c>
       <c r="E19">
-        <v>-9.041</v>
+        <v>-8.814</v>
       </c>
       <c r="F19">
-        <v>3.859000000000001</v>
+        <v>4.086000000000001</v>
       </c>
       <c r="G19">
         <v>0.341</v>
@@ -2833,28 +2833,28 @@
         <v>2.29</v>
       </c>
       <c r="M19">
-        <v>0.1998962000000001</v>
+        <v>0.2116548000000001</v>
       </c>
       <c r="N19">
-        <v>2.0901038</v>
+        <v>2.0783452</v>
       </c>
       <c r="O19">
-        <v>0.52252595</v>
+        <v>0.5195862999999999</v>
       </c>
       <c r="P19">
-        <v>1.56757785</v>
+        <v>1.5587589</v>
       </c>
       <c r="Q19">
-        <v>3.89757785</v>
+        <v>3.8887589</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1259445580933213</v>
+        <v>0.1267101241452858</v>
       </c>
       <c r="T19">
-        <v>1.562166610226365</v>
+        <v>1.577088917526496</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.45594563578497</v>
+        <v>10.81950421157469</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1108953017991343</v>
+        <v>0.110652120380812</v>
       </c>
       <c r="C20">
-        <v>21.8162782419433</v>
+        <v>21.6306396720427</v>
       </c>
       <c r="D20">
-        <v>25.5612782419433</v>
+        <v>25.6026396720427</v>
       </c>
       <c r="E20">
-        <v>-8.814</v>
+        <v>-8.587</v>
       </c>
       <c r="F20">
-        <v>4.086</v>
+        <v>4.313000000000001</v>
       </c>
       <c r="G20">
         <v>0.341</v>
@@ -2915,28 +2915,28 @@
         <v>2.29</v>
       </c>
       <c r="M20">
-        <v>0.2116548</v>
+        <v>0.2234134</v>
       </c>
       <c r="N20">
-        <v>2.0783452</v>
+        <v>2.0665866</v>
       </c>
       <c r="O20">
-        <v>0.5195863000000001</v>
+        <v>0.51664665</v>
       </c>
       <c r="P20">
-        <v>1.5587589</v>
+        <v>1.54993995</v>
       </c>
       <c r="Q20">
-        <v>3.8887589</v>
+        <v>3.87993995</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1267101241452858</v>
+        <v>0.1274945930627308</v>
       </c>
       <c r="T20">
-        <v>1.577088917526496</v>
+        <v>1.592379676858729</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.8195042115747</v>
+        <v>10.25005662149182</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.110652120380812</v>
+        <v>0.1106639389624896</v>
       </c>
       <c r="C21">
-        <v>21.6306396720427</v>
+        <v>21.40162641816357</v>
       </c>
       <c r="D21">
-        <v>25.6026396720427</v>
+        <v>25.60062641816356</v>
       </c>
       <c r="E21">
-        <v>-8.587</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="F21">
-        <v>4.313000000000001</v>
+        <v>4.540000000000001</v>
       </c>
       <c r="G21">
         <v>0.341</v>
@@ -2997,45 +2997,45 @@
         <v>2.29</v>
       </c>
       <c r="M21">
-        <v>0.2234134</v>
+        <v>0.2428900000000001</v>
       </c>
       <c r="N21">
-        <v>2.0665866</v>
+        <v>2.04711</v>
       </c>
       <c r="O21">
-        <v>0.51664665</v>
+        <v>0.5117775</v>
       </c>
       <c r="P21">
-        <v>1.54993995</v>
+        <v>1.5353325</v>
       </c>
       <c r="Q21">
-        <v>3.87993995</v>
+        <v>3.8653325</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1274945930627308</v>
+        <v>0.128298673703112</v>
       </c>
       <c r="T21">
-        <v>1.592379676858729</v>
+        <v>1.608052705174267</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.25005662149182</v>
+        <v>9.428136193338547</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1106639389624896</v>
+        <v>0.1104335075441673</v>
       </c>
       <c r="C22">
-        <v>21.40162641816357</v>
+        <v>21.21393678373417</v>
       </c>
       <c r="D22">
-        <v>25.60062641816356</v>
+        <v>25.63993678373417</v>
       </c>
       <c r="E22">
-        <v>-8.359999999999999</v>
+        <v>-8.132999999999999</v>
       </c>
       <c r="F22">
-        <v>4.540000000000001</v>
+        <v>4.767000000000001</v>
       </c>
       <c r="G22">
         <v>0.341</v>
@@ -3079,28 +3079,28 @@
         <v>2.29</v>
       </c>
       <c r="M22">
-        <v>0.2428900000000001</v>
+        <v>0.2550345000000001</v>
       </c>
       <c r="N22">
-        <v>2.04711</v>
+        <v>2.0349655</v>
       </c>
       <c r="O22">
-        <v>0.5117775</v>
+        <v>0.5087413750000001</v>
       </c>
       <c r="P22">
-        <v>1.5353325</v>
+        <v>1.526224125</v>
       </c>
       <c r="Q22">
-        <v>3.8653325</v>
+        <v>3.856224125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.128298673703112</v>
+        <v>0.1291231108154016</v>
       </c>
       <c r="T22">
-        <v>1.608052705174267</v>
+        <v>1.624122519016782</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.428136193338547</v>
+        <v>8.979177326989092</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1104335075441673</v>
+        <v>0.110203076125845</v>
       </c>
       <c r="C23">
-        <v>21.21393678373417</v>
+        <v>21.02636805895107</v>
       </c>
       <c r="D23">
-        <v>25.63993678373417</v>
+        <v>25.67936805895107</v>
       </c>
       <c r="E23">
-        <v>-8.132999999999999</v>
+        <v>-7.906</v>
       </c>
       <c r="F23">
-        <v>4.767</v>
+        <v>4.994000000000001</v>
       </c>
       <c r="G23">
         <v>0.341</v>
@@ -3161,28 +3161,28 @@
         <v>2.29</v>
       </c>
       <c r="M23">
-        <v>0.2550345</v>
+        <v>0.2671790000000001</v>
       </c>
       <c r="N23">
-        <v>2.0349655</v>
+        <v>2.022821</v>
       </c>
       <c r="O23">
-        <v>0.5087413750000001</v>
+        <v>0.50570525</v>
       </c>
       <c r="P23">
-        <v>1.526224125</v>
+        <v>1.51711575</v>
       </c>
       <c r="Q23">
-        <v>3.856224125</v>
+        <v>3.84711575</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1291231108154016</v>
+        <v>0.1299686873408269</v>
       </c>
       <c r="T23">
-        <v>1.624122519016782</v>
+        <v>1.640604379368078</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.979177326989095</v>
+        <v>8.571032903035043</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.110203076125845</v>
+        <v>0.1099726447075226</v>
       </c>
       <c r="C24">
-        <v>21.02636805895107</v>
+        <v>20.83892080250886</v>
       </c>
       <c r="D24">
-        <v>25.67936805895107</v>
+        <v>25.71892080250886</v>
       </c>
       <c r="E24">
-        <v>-7.906</v>
+        <v>-7.678999999999999</v>
       </c>
       <c r="F24">
-        <v>4.994000000000001</v>
+        <v>5.221000000000001</v>
       </c>
       <c r="G24">
         <v>0.341</v>
@@ -3243,28 +3243,28 @@
         <v>2.29</v>
       </c>
       <c r="M24">
-        <v>0.2671790000000001</v>
+        <v>0.2793235000000001</v>
       </c>
       <c r="N24">
-        <v>2.022821</v>
+        <v>2.0106765</v>
       </c>
       <c r="O24">
-        <v>0.50570525</v>
+        <v>0.5026691249999999</v>
       </c>
       <c r="P24">
-        <v>1.51711575</v>
+        <v>1.508007375</v>
       </c>
       <c r="Q24">
-        <v>3.84711575</v>
+        <v>3.838007375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1299686873408269</v>
+        <v>0.1308362268928865</v>
       </c>
       <c r="T24">
-        <v>1.640604379368078</v>
+        <v>1.65751433998824</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.571032903035043</v>
+        <v>8.198379298555256</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1099726447075226</v>
+        <v>0.1097422132892003</v>
       </c>
       <c r="C25">
-        <v>20.83892080250886</v>
+        <v>20.65159557654962</v>
       </c>
       <c r="D25">
-        <v>25.71892080250886</v>
+        <v>25.75859557654962</v>
       </c>
       <c r="E25">
-        <v>-7.678999999999999</v>
+        <v>-7.451999999999999</v>
       </c>
       <c r="F25">
-        <v>5.221000000000001</v>
+        <v>5.448000000000001</v>
       </c>
       <c r="G25">
         <v>0.341</v>
@@ -3325,28 +3325,28 @@
         <v>2.29</v>
       </c>
       <c r="M25">
-        <v>0.2793235000000001</v>
+        <v>0.2914680000000001</v>
       </c>
       <c r="N25">
-        <v>2.0106765</v>
+        <v>1.998532</v>
       </c>
       <c r="O25">
-        <v>0.5026691249999999</v>
+        <v>0.499633</v>
       </c>
       <c r="P25">
-        <v>1.508007375</v>
+        <v>1.498899</v>
       </c>
       <c r="Q25">
-        <v>3.838007375</v>
+        <v>3.828899</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1308362268928865</v>
+        <v>0.1317265964331583</v>
       </c>
       <c r="T25">
-        <v>1.65751433998824</v>
+        <v>1.67486929957209</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.198379298555256</v>
+        <v>7.856780161115456</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1097422132892003</v>
+        <v>0.1096617818708779</v>
       </c>
       <c r="C26">
-        <v>20.65159557654962</v>
+        <v>20.43847277645828</v>
       </c>
       <c r="D26">
-        <v>25.75859557654962</v>
+        <v>25.77247277645828</v>
       </c>
       <c r="E26">
-        <v>-7.452</v>
+        <v>-7.225</v>
       </c>
       <c r="F26">
-        <v>5.448</v>
+        <v>5.675000000000001</v>
       </c>
       <c r="G26">
         <v>0.341</v>
@@ -3407,45 +3407,45 @@
         <v>2.29</v>
       </c>
       <c r="M26">
-        <v>0.291468</v>
+        <v>0.3081525000000001</v>
       </c>
       <c r="N26">
-        <v>1.998532</v>
+        <v>1.9818475</v>
       </c>
       <c r="O26">
-        <v>0.499633</v>
+        <v>0.495461875</v>
       </c>
       <c r="P26">
-        <v>1.498899</v>
+        <v>1.486385625</v>
       </c>
       <c r="Q26">
-        <v>3.828899</v>
+        <v>3.816385625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1317265964331583</v>
+        <v>0.1326407091611706</v>
       </c>
       <c r="T26">
-        <v>1.67486929957209</v>
+        <v>1.692687058078176</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.856780161115457</v>
+        <v>7.431385434160033</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1096617818708779</v>
+        <v>0.1094373504525556</v>
       </c>
       <c r="C27">
-        <v>20.43847277645828</v>
+        <v>20.25027414419042</v>
       </c>
       <c r="D27">
-        <v>25.77247277645828</v>
+        <v>25.81127414419042</v>
       </c>
       <c r="E27">
-        <v>-7.225</v>
+        <v>-6.997999999999999</v>
       </c>
       <c r="F27">
-        <v>5.675000000000001</v>
+        <v>5.902000000000001</v>
       </c>
       <c r="G27">
         <v>0.341</v>
@@ -3489,28 +3489,28 @@
         <v>2.29</v>
       </c>
       <c r="M27">
-        <v>0.3081525000000001</v>
+        <v>0.3204786000000001</v>
       </c>
       <c r="N27">
-        <v>1.9818475</v>
+        <v>1.9695214</v>
       </c>
       <c r="O27">
-        <v>0.495461875</v>
+        <v>0.49238035</v>
       </c>
       <c r="P27">
-        <v>1.486385625</v>
+        <v>1.47714105</v>
       </c>
       <c r="Q27">
-        <v>3.816385625</v>
+        <v>3.80714105</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1326407091611706</v>
+        <v>0.1335795276385887</v>
       </c>
       <c r="T27">
-        <v>1.692687058078176</v>
+        <v>1.710986377624967</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.431385434160033</v>
+        <v>7.145562917461571</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1094373504525556</v>
+        <v>0.1092129190342332</v>
       </c>
       <c r="C28">
-        <v>20.25027414419042</v>
+        <v>20.06219252174321</v>
       </c>
       <c r="D28">
-        <v>25.81127414419042</v>
+        <v>25.85019252174321</v>
       </c>
       <c r="E28">
-        <v>-6.997999999999999</v>
+        <v>-6.770999999999999</v>
       </c>
       <c r="F28">
-        <v>5.902000000000001</v>
+        <v>6.129000000000001</v>
       </c>
       <c r="G28">
         <v>0.341</v>
@@ -3571,28 +3571,28 @@
         <v>2.29</v>
       </c>
       <c r="M28">
-        <v>0.3204786000000001</v>
+        <v>0.3328047000000001</v>
       </c>
       <c r="N28">
-        <v>1.9695214</v>
+        <v>1.9571953</v>
       </c>
       <c r="O28">
-        <v>0.49238035</v>
+        <v>0.489298825</v>
       </c>
       <c r="P28">
-        <v>1.47714105</v>
+        <v>1.467896475</v>
       </c>
       <c r="Q28">
-        <v>3.80714105</v>
+        <v>3.797896475</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1335795276385887</v>
+        <v>0.1345440671701825</v>
       </c>
       <c r="T28">
-        <v>1.710986377624967</v>
+        <v>1.729787048392218</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.145562917461571</v>
+        <v>6.880912439037068</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1092129190342332</v>
+        <v>0.1089884876159109</v>
       </c>
       <c r="C29">
-        <v>20.06219252174321</v>
+        <v>19.87422843919999</v>
       </c>
       <c r="D29">
-        <v>25.85019252174321</v>
+        <v>25.88922843919999</v>
       </c>
       <c r="E29">
-        <v>-6.770999999999999</v>
+        <v>-6.543999999999999</v>
       </c>
       <c r="F29">
-        <v>6.129000000000001</v>
+        <v>6.356000000000002</v>
       </c>
       <c r="G29">
         <v>0.341</v>
@@ -3653,28 +3653,28 @@
         <v>2.29</v>
       </c>
       <c r="M29">
-        <v>0.3328047000000001</v>
+        <v>0.3451308000000001</v>
       </c>
       <c r="N29">
-        <v>1.9571953</v>
+        <v>1.9448692</v>
       </c>
       <c r="O29">
-        <v>0.489298825</v>
+        <v>0.4862173</v>
       </c>
       <c r="P29">
-        <v>1.467896475</v>
+        <v>1.4586519</v>
       </c>
       <c r="Q29">
-        <v>3.797896475</v>
+        <v>3.7886519</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1345440671701825</v>
+        <v>0.1355353994665429</v>
       </c>
       <c r="T29">
-        <v>1.729787048392218</v>
+        <v>1.749109960014115</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.880912439037068</v>
+        <v>6.635165566214315</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1089884876159109</v>
+        <v>0.1087640561975886</v>
       </c>
       <c r="C30">
-        <v>19.87422843919999</v>
+        <v>19.68638242985086</v>
       </c>
       <c r="D30">
-        <v>25.88922843919999</v>
+        <v>25.92838242985086</v>
       </c>
       <c r="E30">
-        <v>-6.543999999999999</v>
+        <v>-6.316999999999998</v>
       </c>
       <c r="F30">
-        <v>6.356000000000002</v>
+        <v>6.583000000000002</v>
       </c>
       <c r="G30">
         <v>0.341</v>
@@ -3735,28 +3735,28 @@
         <v>2.29</v>
       </c>
       <c r="M30">
-        <v>0.3451308000000001</v>
+        <v>0.3574569000000001</v>
       </c>
       <c r="N30">
-        <v>1.9448692</v>
+        <v>1.9325431</v>
       </c>
       <c r="O30">
-        <v>0.4862173</v>
+        <v>0.483135775</v>
       </c>
       <c r="P30">
-        <v>1.4586519</v>
+        <v>1.449407325</v>
       </c>
       <c r="Q30">
-        <v>3.7886519</v>
+        <v>3.779407325</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1355353994665429</v>
+        <v>0.1365546566163219</v>
       </c>
       <c r="T30">
-        <v>1.749109960014115</v>
+        <v>1.768977179005643</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.635165566214315</v>
+        <v>6.406366753586235</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1087640561975885</v>
+        <v>0.1085396247792662</v>
       </c>
       <c r="C31">
-        <v>19.68638242985086</v>
+        <v>19.49865503021691</v>
       </c>
       <c r="D31">
-        <v>25.92838242985086</v>
+        <v>25.96765503021691</v>
       </c>
       <c r="E31">
-        <v>-6.317</v>
+        <v>-6.09</v>
       </c>
       <c r="F31">
-        <v>6.583</v>
+        <v>6.81</v>
       </c>
       <c r="G31">
         <v>0.341</v>
@@ -3817,28 +3817,28 @@
         <v>2.29</v>
       </c>
       <c r="M31">
-        <v>0.3574569</v>
+        <v>0.369783</v>
       </c>
       <c r="N31">
-        <v>1.9325431</v>
+        <v>1.920217</v>
       </c>
       <c r="O31">
-        <v>0.483135775</v>
+        <v>0.48005425</v>
       </c>
       <c r="P31">
-        <v>1.449407325</v>
+        <v>1.44016275</v>
       </c>
       <c r="Q31">
-        <v>3.779407325</v>
+        <v>3.77016275</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1365546566163219</v>
+        <v>0.1376030353989517</v>
       </c>
       <c r="T31">
-        <v>1.768977179005643</v>
+        <v>1.7894120328255</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.406366753586236</v>
+        <v>6.192821195133361</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1085396247792662</v>
+        <v>0.1085476933609439</v>
       </c>
       <c r="C32">
-        <v>19.49865503021691</v>
+        <v>19.27024107105927</v>
       </c>
       <c r="D32">
-        <v>25.96765503021691</v>
+        <v>25.96624107105927</v>
       </c>
       <c r="E32">
-        <v>-6.09</v>
+        <v>-5.863</v>
       </c>
       <c r="F32">
-        <v>6.81</v>
+        <v>7.037000000000001</v>
       </c>
       <c r="G32">
         <v>0.341</v>
@@ -3899,45 +3899,45 @@
         <v>2.29</v>
       </c>
       <c r="M32">
-        <v>0.369783</v>
+        <v>0.3891461000000001</v>
       </c>
       <c r="N32">
-        <v>1.920217</v>
+        <v>1.9008539</v>
       </c>
       <c r="O32">
-        <v>0.48005425</v>
+        <v>0.475213475</v>
       </c>
       <c r="P32">
-        <v>1.44016275</v>
+        <v>1.425640425</v>
       </c>
       <c r="Q32">
-        <v>3.77016275</v>
+        <v>3.755640425</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1376030353989517</v>
+        <v>0.1386818019723824</v>
       </c>
       <c r="T32">
-        <v>1.7894120328255</v>
+        <v>1.810439201248832</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.192821195133361</v>
+        <v>5.884679301681296</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1085476933609439</v>
+        <v>0.1083307619426215</v>
       </c>
       <c r="C33">
-        <v>19.27024107105927</v>
+        <v>19.08131035679556</v>
       </c>
       <c r="D33">
-        <v>25.96624107105927</v>
+        <v>26.00431035679556</v>
       </c>
       <c r="E33">
-        <v>-5.863</v>
+        <v>-5.635999999999999</v>
       </c>
       <c r="F33">
-        <v>7.037000000000001</v>
+        <v>7.264000000000001</v>
       </c>
       <c r="G33">
         <v>0.341</v>
@@ -3981,28 +3981,28 @@
         <v>2.29</v>
       </c>
       <c r="M33">
-        <v>0.3891461000000001</v>
+        <v>0.4016992000000001</v>
       </c>
       <c r="N33">
-        <v>1.9008539</v>
+        <v>1.8883008</v>
       </c>
       <c r="O33">
-        <v>0.475213475</v>
+        <v>0.4720752</v>
       </c>
       <c r="P33">
-        <v>1.425640425</v>
+        <v>1.4162256</v>
       </c>
       <c r="Q33">
-        <v>3.755640425</v>
+        <v>3.7462256</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1386818019723824</v>
+        <v>0.1397922969744435</v>
       </c>
       <c r="T33">
-        <v>1.810439201248832</v>
+        <v>1.832084815802261</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.884679301681296</v>
+        <v>5.700783073503755</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1083307619426215</v>
+        <v>0.1081138305242992</v>
       </c>
       <c r="C34">
-        <v>19.08131035679556</v>
+        <v>18.89249143371624</v>
       </c>
       <c r="D34">
-        <v>26.00431035679556</v>
+        <v>26.04249143371625</v>
       </c>
       <c r="E34">
-        <v>-5.635999999999999</v>
+        <v>-5.408999999999999</v>
       </c>
       <c r="F34">
-        <v>7.264000000000001</v>
+        <v>7.491000000000001</v>
       </c>
       <c r="G34">
         <v>0.341</v>
@@ -4063,28 +4063,28 @@
         <v>2.29</v>
       </c>
       <c r="M34">
-        <v>0.4016992000000001</v>
+        <v>0.4142523000000001</v>
       </c>
       <c r="N34">
-        <v>1.8883008</v>
+        <v>1.8757477</v>
       </c>
       <c r="O34">
-        <v>0.4720752</v>
+        <v>0.468936925</v>
       </c>
       <c r="P34">
-        <v>1.4162256</v>
+        <v>1.406810775</v>
       </c>
       <c r="Q34">
-        <v>3.7462256</v>
+        <v>3.736810775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1397922969744435</v>
+        <v>0.1409359410810436</v>
       </c>
       <c r="T34">
-        <v>1.832084815802261</v>
+        <v>1.854376568103554</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.700783073503755</v>
+        <v>5.528032071276368</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1081138305242992</v>
+        <v>0.1078968991059769</v>
       </c>
       <c r="C35">
-        <v>18.89249143371624</v>
+        <v>18.7037847949608</v>
       </c>
       <c r="D35">
-        <v>26.04249143371625</v>
+        <v>26.0807847949608</v>
       </c>
       <c r="E35">
-        <v>-5.408999999999999</v>
+        <v>-5.181999999999999</v>
       </c>
       <c r="F35">
-        <v>7.491000000000001</v>
+        <v>7.718000000000002</v>
       </c>
       <c r="G35">
         <v>0.341</v>
@@ -4145,28 +4145,28 @@
         <v>2.29</v>
       </c>
       <c r="M35">
-        <v>0.4142523000000001</v>
+        <v>0.4268054000000001</v>
       </c>
       <c r="N35">
-        <v>1.8757477</v>
+        <v>1.8631946</v>
       </c>
       <c r="O35">
-        <v>0.468936925</v>
+        <v>0.46579865</v>
       </c>
       <c r="P35">
-        <v>1.406810775</v>
+        <v>1.39739595</v>
       </c>
       <c r="Q35">
-        <v>3.736810775</v>
+        <v>3.72739595</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1409359410810436</v>
+        <v>0.1421142410696619</v>
       </c>
       <c r="T35">
-        <v>1.854376568103554</v>
+        <v>1.877343828050341</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.528032071276368</v>
+        <v>5.365442892709416</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1078968991059769</v>
+        <v>0.1076799676876545</v>
       </c>
       <c r="C36">
-        <v>18.7037847949608</v>
+        <v>18.51519093657346</v>
       </c>
       <c r="D36">
-        <v>26.0807847949608</v>
+        <v>26.11919093657346</v>
       </c>
       <c r="E36">
-        <v>-5.181999999999999</v>
+        <v>-4.954999999999998</v>
       </c>
       <c r="F36">
-        <v>7.718000000000002</v>
+        <v>7.945000000000002</v>
       </c>
       <c r="G36">
         <v>0.341</v>
@@ -4227,28 +4227,28 @@
         <v>2.29</v>
       </c>
       <c r="M36">
-        <v>0.4268054000000001</v>
+        <v>0.4393585000000002</v>
       </c>
       <c r="N36">
-        <v>1.8631946</v>
+        <v>1.8506415</v>
       </c>
       <c r="O36">
-        <v>0.46579865</v>
+        <v>0.462660375</v>
       </c>
       <c r="P36">
-        <v>1.39739595</v>
+        <v>1.387981125</v>
       </c>
       <c r="Q36">
-        <v>3.72739595</v>
+        <v>3.717981125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1421142410696619</v>
+        <v>0.1433287964425454</v>
       </c>
       <c r="T36">
-        <v>1.877343828050341</v>
+        <v>1.901017772918567</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.365442892709416</v>
+        <v>5.212144524346289</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1076799676876545</v>
+        <v>0.1074630362693322</v>
       </c>
       <c r="C37">
-        <v>18.51519093657346</v>
+        <v>18.32671035752462</v>
       </c>
       <c r="D37">
-        <v>26.11919093657346</v>
+        <v>26.15771035752462</v>
       </c>
       <c r="E37">
-        <v>-4.954999999999998</v>
+        <v>-4.727999999999998</v>
       </c>
       <c r="F37">
-        <v>7.945000000000002</v>
+        <v>8.172000000000002</v>
       </c>
       <c r="G37">
         <v>0.341</v>
@@ -4309,28 +4309,28 @@
         <v>2.29</v>
       </c>
       <c r="M37">
-        <v>0.4393585000000002</v>
+        <v>0.4519116000000001</v>
       </c>
       <c r="N37">
-        <v>1.8506415</v>
+        <v>1.8380884</v>
       </c>
       <c r="O37">
-        <v>0.462660375</v>
+        <v>0.4595221</v>
       </c>
       <c r="P37">
-        <v>1.387981125</v>
+        <v>1.3785663</v>
       </c>
       <c r="Q37">
-        <v>3.717981125</v>
+        <v>3.7085663</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1433287964425454</v>
+        <v>0.1445813066708315</v>
       </c>
       <c r="T37">
-        <v>1.901017772918567</v>
+        <v>1.925431528563925</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.212144524346289</v>
+        <v>5.067362732003337</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1074630362693322</v>
+        <v>0.1072461048510098</v>
       </c>
       <c r="C38">
-        <v>18.32671035752462</v>
+        <v>18.1383435597325</v>
       </c>
       <c r="D38">
-        <v>26.15771035752462</v>
+        <v>26.1963435597325</v>
       </c>
       <c r="E38">
-        <v>-4.728</v>
+        <v>-4.500999999999999</v>
       </c>
       <c r="F38">
-        <v>8.172000000000001</v>
+        <v>8.399000000000001</v>
       </c>
       <c r="G38">
         <v>0.341</v>
@@ -4391,28 +4391,28 @@
         <v>2.29</v>
       </c>
       <c r="M38">
-        <v>0.4519116</v>
+        <v>0.4644647000000001</v>
       </c>
       <c r="N38">
-        <v>1.8380884</v>
+        <v>1.8255353</v>
       </c>
       <c r="O38">
-        <v>0.4595221</v>
+        <v>0.456383825</v>
       </c>
       <c r="P38">
-        <v>1.3785663</v>
+        <v>1.369151475</v>
       </c>
       <c r="Q38">
-        <v>3.7085663</v>
+        <v>3.699151475</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1445813066708315</v>
+        <v>0.145873579128587</v>
       </c>
       <c r="T38">
-        <v>1.925431528563925</v>
+        <v>1.950620324071041</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.067362732003338</v>
+        <v>4.930406982489734</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1072461048510098</v>
+        <v>0.1070291734326875</v>
       </c>
       <c r="C39">
-        <v>18.1383435597325</v>
+        <v>17.95009104808486</v>
       </c>
       <c r="D39">
-        <v>26.1963435597325</v>
+        <v>26.23509104808486</v>
       </c>
       <c r="E39">
-        <v>-4.500999999999999</v>
+        <v>-4.273999999999999</v>
       </c>
       <c r="F39">
-        <v>8.399000000000001</v>
+        <v>8.626000000000001</v>
       </c>
       <c r="G39">
         <v>0.341</v>
@@ -4473,28 +4473,28 @@
         <v>2.29</v>
       </c>
       <c r="M39">
-        <v>0.4644647000000001</v>
+        <v>0.4770178000000001</v>
       </c>
       <c r="N39">
-        <v>1.8255353</v>
+        <v>1.8129822</v>
       </c>
       <c r="O39">
-        <v>0.456383825</v>
+        <v>0.45324555</v>
       </c>
       <c r="P39">
-        <v>1.369151475</v>
+        <v>1.35973665</v>
       </c>
       <c r="Q39">
-        <v>3.699151475</v>
+        <v>3.68973665</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.145873579128587</v>
+        <v>0.1472075377946573</v>
       </c>
       <c r="T39">
-        <v>1.950620324071041</v>
+        <v>1.976621661368709</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.930406982489734</v>
+        <v>4.800659430318952</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1070291734326875</v>
+        <v>0.1068122420143651</v>
       </c>
       <c r="C40">
-        <v>17.95009104808486</v>
+        <v>17.76195333046107</v>
       </c>
       <c r="D40">
-        <v>26.23509104808486</v>
+        <v>26.27395333046107</v>
       </c>
       <c r="E40">
-        <v>-4.273999999999999</v>
+        <v>-4.046999999999999</v>
       </c>
       <c r="F40">
-        <v>8.626000000000001</v>
+        <v>8.853000000000002</v>
       </c>
       <c r="G40">
         <v>0.341</v>
@@ -4555,28 +4555,28 @@
         <v>2.29</v>
       </c>
       <c r="M40">
-        <v>0.4770178000000001</v>
+        <v>0.4895709000000001</v>
       </c>
       <c r="N40">
-        <v>1.8129822</v>
+        <v>1.8004291</v>
       </c>
       <c r="O40">
-        <v>0.45324555</v>
+        <v>0.450107275</v>
       </c>
       <c r="P40">
-        <v>1.35973665</v>
+        <v>1.350321825</v>
       </c>
       <c r="Q40">
-        <v>3.68973665</v>
+        <v>3.680321825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1472075377946573</v>
+        <v>0.1485852328104347</v>
       </c>
       <c r="T40">
-        <v>1.976621661368709</v>
+        <v>2.003475501528595</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.800659430318952</v>
+        <v>4.677565598772311</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1068122420143651</v>
+        <v>0.1065953105960428</v>
       </c>
       <c r="C41">
-        <v>17.76195333046107</v>
+        <v>17.57393091775426</v>
       </c>
       <c r="D41">
-        <v>26.27395333046107</v>
+        <v>26.31293091775426</v>
       </c>
       <c r="E41">
-        <v>-4.046999999999999</v>
+        <v>-3.819999999999999</v>
       </c>
       <c r="F41">
-        <v>8.853000000000002</v>
+        <v>9.080000000000002</v>
       </c>
       <c r="G41">
         <v>0.341</v>
@@ -4637,28 +4637,28 @@
         <v>2.29</v>
       </c>
       <c r="M41">
-        <v>0.4895709000000001</v>
+        <v>0.5021240000000001</v>
       </c>
       <c r="N41">
-        <v>1.8004291</v>
+        <v>1.787876</v>
       </c>
       <c r="O41">
-        <v>0.450107275</v>
+        <v>0.4469689999999999</v>
       </c>
       <c r="P41">
-        <v>1.350321825</v>
+        <v>1.340907</v>
       </c>
       <c r="Q41">
-        <v>3.680321825</v>
+        <v>3.670907</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1485852328104347</v>
+        <v>0.1500088509934047</v>
       </c>
       <c r="T41">
-        <v>2.003475501528595</v>
+        <v>2.031224469693811</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.677565598772311</v>
+        <v>4.560626458803004</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1065953105960428</v>
+        <v>0.1071471291777205</v>
       </c>
       <c r="C42">
-        <v>17.57393091775426</v>
+        <v>17.24800802184798</v>
       </c>
       <c r="D42">
-        <v>26.31293091775426</v>
+        <v>26.21400802184798</v>
       </c>
       <c r="E42">
-        <v>-3.819999999999999</v>
+        <v>-3.592999999999998</v>
       </c>
       <c r="F42">
-        <v>9.080000000000002</v>
+        <v>9.307000000000002</v>
       </c>
       <c r="G42">
         <v>0.341</v>
@@ -4719,45 +4719,45 @@
         <v>2.29</v>
       </c>
       <c r="M42">
-        <v>0.5021240000000001</v>
+        <v>0.5379446000000002</v>
       </c>
       <c r="N42">
-        <v>1.787876</v>
+        <v>1.7520554</v>
       </c>
       <c r="O42">
-        <v>0.4469689999999999</v>
+        <v>0.4380138499999999</v>
       </c>
       <c r="P42">
-        <v>1.340907</v>
+        <v>1.31404155</v>
       </c>
       <c r="Q42">
-        <v>3.670907</v>
+        <v>3.64404155</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1500088509934047</v>
+        <v>0.1514807274198652</v>
       </c>
       <c r="T42">
-        <v>2.031224469693811</v>
+        <v>2.059914080847679</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.560626458803004</v>
+        <v>4.256943930657542</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1071471291777205</v>
+        <v>0.1069489477593981</v>
       </c>
       <c r="C43">
-        <v>17.24800802184798</v>
+        <v>17.05644971090133</v>
       </c>
       <c r="D43">
-        <v>26.21400802184798</v>
+        <v>26.24944971090133</v>
       </c>
       <c r="E43">
-        <v>-3.592999999999998</v>
+        <v>-3.365999999999998</v>
       </c>
       <c r="F43">
-        <v>9.307000000000002</v>
+        <v>9.534000000000002</v>
       </c>
       <c r="G43">
         <v>0.341</v>
@@ -4801,28 +4801,28 @@
         <v>2.29</v>
       </c>
       <c r="M43">
-        <v>0.5379446000000002</v>
+        <v>0.5510652000000001</v>
       </c>
       <c r="N43">
-        <v>1.7520554</v>
+        <v>1.7389348</v>
       </c>
       <c r="O43">
-        <v>0.4380138499999999</v>
+        <v>0.4347337</v>
       </c>
       <c r="P43">
-        <v>1.31404155</v>
+        <v>1.3042011</v>
       </c>
       <c r="Q43">
-        <v>3.64404155</v>
+        <v>3.6342011</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1514807274198652</v>
+        <v>0.1530033582058588</v>
       </c>
       <c r="T43">
-        <v>2.059914080847679</v>
+        <v>2.089592988937886</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.256943930657542</v>
+        <v>4.155588122784744</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1069489477593981</v>
+        <v>0.1067507663410758</v>
       </c>
       <c r="C44">
-        <v>17.05644971090132</v>
+        <v>16.86498736497483</v>
       </c>
       <c r="D44">
-        <v>26.24944971090132</v>
+        <v>26.28498736497483</v>
       </c>
       <c r="E44">
-        <v>-3.366</v>
+        <v>-3.138999999999999</v>
       </c>
       <c r="F44">
-        <v>9.534000000000001</v>
+        <v>9.761000000000001</v>
       </c>
       <c r="G44">
         <v>0.341</v>
@@ -4883,28 +4883,28 @@
         <v>2.29</v>
       </c>
       <c r="M44">
-        <v>0.5510652</v>
+        <v>0.5641858000000001</v>
       </c>
       <c r="N44">
-        <v>1.7389348</v>
+        <v>1.7258142</v>
       </c>
       <c r="O44">
-        <v>0.4347337</v>
+        <v>0.43145355</v>
       </c>
       <c r="P44">
-        <v>1.3042011</v>
+        <v>1.29436065</v>
       </c>
       <c r="Q44">
-        <v>3.6342011</v>
+        <v>3.62436065</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1530033582058588</v>
+        <v>0.1545794146334663</v>
       </c>
       <c r="T44">
-        <v>2.089592988937886</v>
+        <v>2.120313262224241</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.155588122784745</v>
+        <v>4.058946538533936</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1067507663410758</v>
+        <v>0.1077075849227535</v>
       </c>
       <c r="C45">
-        <v>16.86498736497483</v>
+        <v>16.46729522217826</v>
       </c>
       <c r="D45">
-        <v>26.28498736497483</v>
+        <v>26.11429522217826</v>
       </c>
       <c r="E45">
-        <v>-3.138999999999999</v>
+        <v>-2.911999999999999</v>
       </c>
       <c r="F45">
-        <v>9.761000000000001</v>
+        <v>9.988000000000001</v>
       </c>
       <c r="G45">
         <v>0.341</v>
@@ -4965,45 +4965,45 @@
         <v>2.29</v>
       </c>
       <c r="M45">
-        <v>0.5641858000000001</v>
+        <v>0.6122644</v>
       </c>
       <c r="N45">
-        <v>1.7258142</v>
+        <v>1.6777356</v>
       </c>
       <c r="O45">
-        <v>0.43145355</v>
+        <v>0.4194339</v>
       </c>
       <c r="P45">
-        <v>1.29436065</v>
+        <v>1.2583017</v>
       </c>
       <c r="Q45">
-        <v>3.62436065</v>
+        <v>3.5883017</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1545794146334663</v>
+        <v>0.1562117587906311</v>
       </c>
       <c r="T45">
-        <v>2.120313262224241</v>
+        <v>2.152130688127967</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.058946538533936</v>
+        <v>3.740214195043841</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1077075849227535</v>
+        <v>0.1075356535044311</v>
       </c>
       <c r="C46">
-        <v>16.46729522217826</v>
+        <v>16.27080343615907</v>
       </c>
       <c r="D46">
-        <v>26.11429522217826</v>
+        <v>26.14480343615907</v>
       </c>
       <c r="E46">
-        <v>-2.911999999999999</v>
+        <v>-2.684999999999999</v>
       </c>
       <c r="F46">
-        <v>9.988000000000001</v>
+        <v>10.215</v>
       </c>
       <c r="G46">
         <v>0.341</v>
@@ -5047,28 +5047,28 @@
         <v>2.29</v>
       </c>
       <c r="M46">
-        <v>0.6122644</v>
+        <v>0.6261795000000001</v>
       </c>
       <c r="N46">
-        <v>1.6777356</v>
+        <v>1.6638205</v>
       </c>
       <c r="O46">
-        <v>0.4194339</v>
+        <v>0.415955125</v>
       </c>
       <c r="P46">
-        <v>1.2583017</v>
+        <v>1.247865375</v>
       </c>
       <c r="Q46">
-        <v>3.5883017</v>
+        <v>3.577865375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1562117587906311</v>
+        <v>0.1579034609171475</v>
       </c>
       <c r="T46">
-        <v>2.152130688127967</v>
+        <v>2.185105111337282</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.740214195043841</v>
+        <v>3.657098324042866</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1075356535044311</v>
+        <v>0.1073637220861088</v>
       </c>
       <c r="C47">
-        <v>16.27080343615907</v>
+        <v>16.07438301639663</v>
       </c>
       <c r="D47">
-        <v>26.14480343615907</v>
+        <v>26.17538301639663</v>
       </c>
       <c r="E47">
-        <v>-2.684999999999999</v>
+        <v>-2.457999999999998</v>
       </c>
       <c r="F47">
-        <v>10.215</v>
+        <v>10.442</v>
       </c>
       <c r="G47">
         <v>0.341</v>
@@ -5129,28 +5129,28 @@
         <v>2.29</v>
       </c>
       <c r="M47">
-        <v>0.6261795000000001</v>
+        <v>0.6400946000000001</v>
       </c>
       <c r="N47">
-        <v>1.6638205</v>
+        <v>1.6499054</v>
       </c>
       <c r="O47">
-        <v>0.415955125</v>
+        <v>0.41247635</v>
       </c>
       <c r="P47">
-        <v>1.247865375</v>
+        <v>1.23742905</v>
       </c>
       <c r="Q47">
-        <v>3.577865375</v>
+        <v>3.56742905</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1579034609171475</v>
+        <v>0.1596578186779792</v>
       </c>
       <c r="T47">
-        <v>2.185105111337282</v>
+        <v>2.219300809480275</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.657098324042866</v>
+        <v>3.577596186563673</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1073637220861088</v>
+        <v>0.1071917906677864</v>
       </c>
       <c r="C48">
-        <v>16.07438301639663</v>
+        <v>15.87803421359917</v>
       </c>
       <c r="D48">
-        <v>26.17538301639663</v>
+        <v>26.20603421359917</v>
       </c>
       <c r="E48">
-        <v>-2.457999999999998</v>
+        <v>-2.230999999999998</v>
       </c>
       <c r="F48">
-        <v>10.442</v>
+        <v>10.669</v>
       </c>
       <c r="G48">
         <v>0.341</v>
@@ -5211,28 +5211,28 @@
         <v>2.29</v>
       </c>
       <c r="M48">
-        <v>0.6400946000000001</v>
+        <v>0.6540097000000001</v>
       </c>
       <c r="N48">
-        <v>1.6499054</v>
+        <v>1.6359903</v>
       </c>
       <c r="O48">
-        <v>0.41247635</v>
+        <v>0.408997575</v>
       </c>
       <c r="P48">
-        <v>1.23742905</v>
+        <v>1.226992725</v>
       </c>
       <c r="Q48">
-        <v>3.56742905</v>
+        <v>3.556992725</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1596578186779792</v>
+        <v>0.161478378618465</v>
       </c>
       <c r="T48">
-        <v>2.219300809480275</v>
+        <v>2.254786911326778</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.577596186563673</v>
+        <v>3.501477118764446</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1071917906677864</v>
+        <v>0.1080278592494641</v>
       </c>
       <c r="C49">
-        <v>15.87803421359917</v>
+        <v>15.50265387231502</v>
       </c>
       <c r="D49">
-        <v>26.20603421359917</v>
+        <v>26.05765387231503</v>
       </c>
       <c r="E49">
-        <v>-2.230999999999998</v>
+        <v>-2.003999999999998</v>
       </c>
       <c r="F49">
-        <v>10.669</v>
+        <v>10.896</v>
       </c>
       <c r="G49">
         <v>0.341</v>
@@ -5293,45 +5293,45 @@
         <v>2.29</v>
       </c>
       <c r="M49">
-        <v>0.6540097000000001</v>
+        <v>0.6984336000000002</v>
       </c>
       <c r="N49">
-        <v>1.6359903</v>
+        <v>1.5915664</v>
       </c>
       <c r="O49">
-        <v>0.408997575</v>
+        <v>0.3978916</v>
       </c>
       <c r="P49">
-        <v>1.226992725</v>
+        <v>1.1936748</v>
       </c>
       <c r="Q49">
-        <v>3.556992725</v>
+        <v>3.5236748</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.161478378618465</v>
+        <v>0.1633689600951232</v>
       </c>
       <c r="T49">
-        <v>2.254786911326778</v>
+        <v>2.2916378632443</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.501477118764446</v>
+        <v>3.278765511853953</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1080278592494641</v>
+        <v>0.1078769278311418</v>
       </c>
       <c r="C50">
-        <v>15.50265387231503</v>
+        <v>15.30231584393864</v>
       </c>
       <c r="D50">
-        <v>26.05765387231503</v>
+        <v>26.08431584393864</v>
       </c>
       <c r="E50">
-        <v>-2.004</v>
+        <v>-1.776999999999999</v>
       </c>
       <c r="F50">
-        <v>10.896</v>
+        <v>11.123</v>
       </c>
       <c r="G50">
         <v>0.341</v>
@@ -5375,28 +5375,28 @@
         <v>2.29</v>
       </c>
       <c r="M50">
-        <v>0.6984336000000001</v>
+        <v>0.7129843000000001</v>
       </c>
       <c r="N50">
-        <v>1.5915664</v>
+        <v>1.5770157</v>
       </c>
       <c r="O50">
-        <v>0.3978916</v>
+        <v>0.394253925</v>
       </c>
       <c r="P50">
-        <v>1.1936748</v>
+        <v>1.182761775</v>
       </c>
       <c r="Q50">
-        <v>3.5236748</v>
+        <v>3.512761775</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1633689600951232</v>
+        <v>0.1653336820218466</v>
       </c>
       <c r="T50">
-        <v>2.2916378632443</v>
+        <v>2.329933950531136</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.278765511853954</v>
+        <v>3.211851929979384</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1078769278311418</v>
+        <v>0.1077259964128194</v>
       </c>
       <c r="C51">
-        <v>15.30231584393864</v>
+        <v>15.10203243205428</v>
       </c>
       <c r="D51">
-        <v>26.08431584393864</v>
+        <v>26.11103243205428</v>
       </c>
       <c r="E51">
-        <v>-1.776999999999999</v>
+        <v>-1.549999999999999</v>
       </c>
       <c r="F51">
-        <v>11.123</v>
+        <v>11.35</v>
       </c>
       <c r="G51">
         <v>0.341</v>
@@ -5457,28 +5457,28 @@
         <v>2.29</v>
       </c>
       <c r="M51">
-        <v>0.7129843000000001</v>
+        <v>0.7275350000000002</v>
       </c>
       <c r="N51">
-        <v>1.5770157</v>
+        <v>1.562465</v>
       </c>
       <c r="O51">
-        <v>0.394253925</v>
+        <v>0.39061625</v>
       </c>
       <c r="P51">
-        <v>1.182761775</v>
+        <v>1.17184875</v>
       </c>
       <c r="Q51">
-        <v>3.512761775</v>
+        <v>3.50184875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1653336820218466</v>
+        <v>0.1673769928256388</v>
       </c>
       <c r="T51">
-        <v>2.329933950531136</v>
+        <v>2.369761881309446</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.211851929979384</v>
+        <v>3.147614891379796</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1077259964128194</v>
+        <v>0.1075750649944971</v>
       </c>
       <c r="C52">
-        <v>15.10203243205428</v>
+        <v>14.90180380465513</v>
       </c>
       <c r="D52">
-        <v>26.11103243205428</v>
+        <v>26.13780380465513</v>
       </c>
       <c r="E52">
-        <v>-1.549999999999999</v>
+        <v>-1.322999999999999</v>
       </c>
       <c r="F52">
-        <v>11.35</v>
+        <v>11.577</v>
       </c>
       <c r="G52">
         <v>0.341</v>
@@ -5539,28 +5539,28 @@
         <v>2.29</v>
       </c>
       <c r="M52">
-        <v>0.7275350000000002</v>
+        <v>0.7420857000000002</v>
       </c>
       <c r="N52">
-        <v>1.562465</v>
+        <v>1.5479143</v>
       </c>
       <c r="O52">
-        <v>0.39061625</v>
+        <v>0.386978575</v>
       </c>
       <c r="P52">
-        <v>1.17184875</v>
+        <v>1.160935725</v>
       </c>
       <c r="Q52">
-        <v>3.50184875</v>
+        <v>3.490935725</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1673769928256388</v>
+        <v>0.1695037040704022</v>
       </c>
       <c r="T52">
-        <v>2.369761881309446</v>
+        <v>2.411215441915443</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.147614891379796</v>
+        <v>3.085896952333133</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1075750649944971</v>
+        <v>0.1074241335761747</v>
       </c>
       <c r="C53">
-        <v>14.90180380465513</v>
+        <v>14.70163013042405</v>
       </c>
       <c r="D53">
-        <v>26.13780380465513</v>
+        <v>26.16463013042405</v>
       </c>
       <c r="E53">
-        <v>-1.322999999999999</v>
+        <v>-1.095999999999998</v>
       </c>
       <c r="F53">
-        <v>11.577</v>
+        <v>11.804</v>
       </c>
       <c r="G53">
         <v>0.341</v>
@@ -5621,28 +5621,28 @@
         <v>2.29</v>
       </c>
       <c r="M53">
-        <v>0.7420857000000002</v>
+        <v>0.7566364000000002</v>
       </c>
       <c r="N53">
-        <v>1.5479143</v>
+        <v>1.5333636</v>
       </c>
       <c r="O53">
-        <v>0.386978575</v>
+        <v>0.3833409</v>
       </c>
       <c r="P53">
-        <v>1.160935725</v>
+        <v>1.1500227</v>
       </c>
       <c r="Q53">
-        <v>3.490935725</v>
+        <v>3.4800227</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1695037040704022</v>
+        <v>0.1717190282836973</v>
       </c>
       <c r="T53">
-        <v>2.411215441915443</v>
+        <v>2.454396234213355</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.085896952333133</v>
+        <v>3.02655278017288</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1074241335761747</v>
+        <v>0.1103737021578524</v>
       </c>
       <c r="C54">
-        <v>14.70163013042405</v>
+        <v>13.96015900222033</v>
       </c>
       <c r="D54">
-        <v>26.16463013042405</v>
+        <v>25.65015900222033</v>
       </c>
       <c r="E54">
-        <v>-1.095999999999998</v>
+        <v>-0.868999999999998</v>
       </c>
       <c r="F54">
-        <v>11.804</v>
+        <v>12.031</v>
       </c>
       <c r="G54">
         <v>0.341</v>
@@ -5703,45 +5703,45 @@
         <v>2.29</v>
       </c>
       <c r="M54">
-        <v>0.7566364000000002</v>
+        <v>0.8650289000000002</v>
       </c>
       <c r="N54">
-        <v>1.5333636</v>
+        <v>1.4249711</v>
       </c>
       <c r="O54">
-        <v>0.3833409</v>
+        <v>0.356242775</v>
       </c>
       <c r="P54">
-        <v>1.1500227</v>
+        <v>1.068728325</v>
       </c>
       <c r="Q54">
-        <v>3.4800227</v>
+        <v>3.398728325</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1717190282836973</v>
+        <v>0.1740286216124519</v>
       </c>
       <c r="T54">
-        <v>2.454396234213355</v>
+        <v>2.499414507034584</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.02655278017288</v>
+        <v>2.647310396219131</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1103737021578524</v>
+        <v>0.11028127073953</v>
       </c>
       <c r="C55">
-        <v>13.96015900222033</v>
+        <v>13.74897385938329</v>
       </c>
       <c r="D55">
-        <v>25.65015900222033</v>
+        <v>25.66597385938329</v>
       </c>
       <c r="E55">
-        <v>-0.868999999999998</v>
+        <v>-0.6419999999999977</v>
       </c>
       <c r="F55">
-        <v>12.031</v>
+        <v>12.258</v>
       </c>
       <c r="G55">
         <v>0.341</v>
@@ -5785,28 +5785,28 @@
         <v>2.29</v>
       </c>
       <c r="M55">
-        <v>0.8650289000000002</v>
+        <v>0.8813502000000003</v>
       </c>
       <c r="N55">
-        <v>1.4249711</v>
+        <v>1.4086498</v>
       </c>
       <c r="O55">
-        <v>0.356242775</v>
+        <v>0.3521624499999999</v>
       </c>
       <c r="P55">
-        <v>1.068728325</v>
+        <v>1.05648735</v>
       </c>
       <c r="Q55">
-        <v>3.398728325</v>
+        <v>3.38648735</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1740286216124519</v>
+        <v>0.1764386320424566</v>
       </c>
       <c r="T55">
-        <v>2.499414507034584</v>
+        <v>2.54639009606543</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.647310396219131</v>
+        <v>2.598286129622481</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.11028127073953</v>
+        <v>0.1101888393212077</v>
       </c>
       <c r="C56">
-        <v>13.74897385938329</v>
+        <v>13.53780823018823</v>
       </c>
       <c r="D56">
-        <v>25.66597385938329</v>
+        <v>25.68180823018823</v>
       </c>
       <c r="E56">
-        <v>-0.6419999999999977</v>
+        <v>-0.4149999999999974</v>
       </c>
       <c r="F56">
-        <v>12.258</v>
+        <v>12.485</v>
       </c>
       <c r="G56">
         <v>0.341</v>
@@ -5867,28 +5867,28 @@
         <v>2.29</v>
       </c>
       <c r="M56">
-        <v>0.8813502000000003</v>
+        <v>0.8976715000000003</v>
       </c>
       <c r="N56">
-        <v>1.4086498</v>
+        <v>1.3923285</v>
       </c>
       <c r="O56">
-        <v>0.3521624499999999</v>
+        <v>0.3480821249999999</v>
       </c>
       <c r="P56">
-        <v>1.05648735</v>
+        <v>1.044246375</v>
       </c>
       <c r="Q56">
-        <v>3.38648735</v>
+        <v>3.374246375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1764386320424566</v>
+        <v>0.1789557540471282</v>
       </c>
       <c r="T56">
-        <v>2.54639009606543</v>
+        <v>2.595453489053204</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.598286129622481</v>
+        <v>2.551044563629345</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1101888393212077</v>
+        <v>0.1100964079028854</v>
       </c>
       <c r="C57">
-        <v>13.53780823018823</v>
+        <v>13.3266621507737</v>
       </c>
       <c r="D57">
-        <v>25.68180823018823</v>
+        <v>25.6976621507737</v>
       </c>
       <c r="E57">
-        <v>-0.4149999999999974</v>
+        <v>-0.1879999999999971</v>
       </c>
       <c r="F57">
-        <v>12.485</v>
+        <v>12.712</v>
       </c>
       <c r="G57">
         <v>0.341</v>
@@ -5949,28 +5949,28 @@
         <v>2.29</v>
       </c>
       <c r="M57">
-        <v>0.8976715000000003</v>
+        <v>0.9139928000000003</v>
       </c>
       <c r="N57">
-        <v>1.3923285</v>
+        <v>1.3760072</v>
       </c>
       <c r="O57">
-        <v>0.3480821249999999</v>
+        <v>0.3440017999999999</v>
       </c>
       <c r="P57">
-        <v>1.044246375</v>
+        <v>1.0320054</v>
       </c>
       <c r="Q57">
-        <v>3.374246375</v>
+        <v>3.3620054</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1789557540471282</v>
+        <v>0.1815872906883758</v>
       </c>
       <c r="T57">
-        <v>2.595453489053204</v>
+        <v>2.646747036267694</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.551044563629345</v>
+        <v>2.505490196421678</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1100964079028854</v>
+        <v>0.111671226484563</v>
       </c>
       <c r="C58">
-        <v>13.3266621507737</v>
+        <v>12.83219424910253</v>
       </c>
       <c r="D58">
-        <v>25.6976621507737</v>
+        <v>25.43019424910253</v>
       </c>
       <c r="E58">
-        <v>-0.1879999999999971</v>
+        <v>0.03900000000000325</v>
       </c>
       <c r="F58">
-        <v>12.712</v>
+        <v>12.939</v>
       </c>
       <c r="G58">
         <v>0.341</v>
@@ -6031,45 +6031,45 @@
         <v>2.29</v>
       </c>
       <c r="M58">
-        <v>0.9139928000000003</v>
+        <v>0.9807762000000003</v>
       </c>
       <c r="N58">
-        <v>1.3760072</v>
+        <v>1.3092238</v>
       </c>
       <c r="O58">
-        <v>0.3440017999999999</v>
+        <v>0.32730595</v>
       </c>
       <c r="P58">
-        <v>1.0320054</v>
+        <v>0.9819178499999999</v>
       </c>
       <c r="Q58">
-        <v>3.3620054</v>
+        <v>3.31191785</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1815872906883758</v>
+        <v>0.1843412243827047</v>
       </c>
       <c r="T58">
-        <v>2.646747036267694</v>
+        <v>2.700426329864253</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.505490196421678</v>
+        <v>2.334885369363571</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.111671226484563</v>
+        <v>0.1116080450662407</v>
       </c>
       <c r="C59">
-        <v>12.83219424910253</v>
+        <v>12.61581775743451</v>
       </c>
       <c r="D59">
-        <v>25.43019424910253</v>
+        <v>25.44081775743452</v>
       </c>
       <c r="E59">
-        <v>0.03900000000000325</v>
+        <v>0.2660000000000036</v>
       </c>
       <c r="F59">
-        <v>12.939</v>
+        <v>13.166</v>
       </c>
       <c r="G59">
         <v>0.341</v>
@@ -6113,28 +6113,28 @@
         <v>2.29</v>
       </c>
       <c r="M59">
-        <v>0.9807762000000003</v>
+        <v>0.9979828000000004</v>
       </c>
       <c r="N59">
-        <v>1.3092238</v>
+        <v>1.2920172</v>
       </c>
       <c r="O59">
-        <v>0.32730595</v>
+        <v>0.3230042999999999</v>
       </c>
       <c r="P59">
-        <v>0.9819178499999999</v>
+        <v>0.9690128999999997</v>
       </c>
       <c r="Q59">
-        <v>3.31191785</v>
+        <v>3.2990129</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1843412243827047</v>
+        <v>0.1872262977767636</v>
       </c>
       <c r="T59">
-        <v>2.700426329864253</v>
+        <v>2.756661780298745</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.334885369363571</v>
+        <v>2.294628725064198</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1116080450662407</v>
+        <v>0.1115448636479183</v>
       </c>
       <c r="C60">
-        <v>12.61581775743452</v>
+        <v>12.39945014545456</v>
       </c>
       <c r="D60">
-        <v>25.44081775743452</v>
+        <v>25.45145014545456</v>
       </c>
       <c r="E60">
-        <v>0.266</v>
+        <v>0.4930000000000003</v>
       </c>
       <c r="F60">
-        <v>13.166</v>
+        <v>13.393</v>
       </c>
       <c r="G60">
         <v>0.341</v>
@@ -6195,28 +6195,28 @@
         <v>2.29</v>
       </c>
       <c r="M60">
-        <v>0.9979828000000001</v>
+        <v>1.0151894</v>
       </c>
       <c r="N60">
-        <v>1.2920172</v>
+        <v>1.2748106</v>
       </c>
       <c r="O60">
-        <v>0.3230043</v>
+        <v>0.31870265</v>
       </c>
       <c r="P60">
-        <v>0.9690129000000001</v>
+        <v>0.9561079499999999</v>
       </c>
       <c r="Q60">
-        <v>3.2990129</v>
+        <v>3.28610795</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1872262977767635</v>
+        <v>0.1902521064583374</v>
       </c>
       <c r="T60">
-        <v>2.756661780298744</v>
+        <v>2.815640423437356</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.294628725064199</v>
+        <v>2.255736712774976</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1115448636479183</v>
+        <v>0.111481682229596</v>
       </c>
       <c r="C61">
-        <v>12.39945014545456</v>
+        <v>12.18309142430047</v>
       </c>
       <c r="D61">
-        <v>25.45145014545456</v>
+        <v>25.46209142430047</v>
       </c>
       <c r="E61">
-        <v>0.4930000000000003</v>
+        <v>0.7200000000000006</v>
       </c>
       <c r="F61">
-        <v>13.393</v>
+        <v>13.62</v>
       </c>
       <c r="G61">
         <v>0.341</v>
@@ -6277,28 +6277,28 @@
         <v>2.29</v>
       </c>
       <c r="M61">
-        <v>1.0151894</v>
+        <v>1.032396</v>
       </c>
       <c r="N61">
-        <v>1.2748106</v>
+        <v>1.257604</v>
       </c>
       <c r="O61">
-        <v>0.31870265</v>
+        <v>0.314401</v>
       </c>
       <c r="P61">
-        <v>0.9561079499999999</v>
+        <v>0.943203</v>
       </c>
       <c r="Q61">
-        <v>3.28610795</v>
+        <v>3.273203</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1902521064583374</v>
+        <v>0.19342920557399</v>
       </c>
       <c r="T61">
-        <v>2.815640423437356</v>
+        <v>2.877567998732899</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.255736712774976</v>
+        <v>2.218141100895393</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.111481682229596</v>
+        <v>0.1114185008112737</v>
       </c>
       <c r="C62">
-        <v>12.18309142430047</v>
+        <v>11.96674160512871</v>
       </c>
       <c r="D62">
-        <v>25.46209142430047</v>
+        <v>25.47274160512871</v>
       </c>
       <c r="E62">
-        <v>0.7200000000000006</v>
+        <v>0.947000000000001</v>
       </c>
       <c r="F62">
-        <v>13.62</v>
+        <v>13.847</v>
       </c>
       <c r="G62">
         <v>0.341</v>
@@ -6359,28 +6359,28 @@
         <v>2.29</v>
       </c>
       <c r="M62">
-        <v>1.032396</v>
+        <v>1.0496026</v>
       </c>
       <c r="N62">
-        <v>1.257604</v>
+        <v>1.2403974</v>
       </c>
       <c r="O62">
-        <v>0.314401</v>
+        <v>0.3100993499999999</v>
       </c>
       <c r="P62">
-        <v>0.943203</v>
+        <v>0.9302980499999998</v>
       </c>
       <c r="Q62">
-        <v>3.273203</v>
+        <v>3.26029805</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.19342920557399</v>
+        <v>0.1967692328494196</v>
       </c>
       <c r="T62">
-        <v>2.877567998732899</v>
+        <v>2.942671347120522</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.218141100895393</v>
+        <v>2.181778132028255</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1114185008112737</v>
+        <v>0.1113553193929513</v>
       </c>
       <c r="C63">
-        <v>11.96674160512871</v>
+        <v>11.7504006991144</v>
       </c>
       <c r="D63">
-        <v>25.47274160512871</v>
+        <v>25.4834006991144</v>
       </c>
       <c r="E63">
-        <v>0.947000000000001</v>
+        <v>1.174000000000001</v>
       </c>
       <c r="F63">
-        <v>13.847</v>
+        <v>14.074</v>
       </c>
       <c r="G63">
         <v>0.341</v>
@@ -6441,28 +6441,28 @@
         <v>2.29</v>
       </c>
       <c r="M63">
-        <v>1.0496026</v>
+        <v>1.0668092</v>
       </c>
       <c r="N63">
-        <v>1.2403974</v>
+        <v>1.2231908</v>
       </c>
       <c r="O63">
-        <v>0.3100993499999999</v>
+        <v>0.3057977</v>
       </c>
       <c r="P63">
-        <v>0.9302980499999998</v>
+        <v>0.9173930999999999</v>
       </c>
       <c r="Q63">
-        <v>3.26029805</v>
+        <v>3.2473931</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1967692328494196</v>
+        <v>0.2002850510340824</v>
       </c>
       <c r="T63">
-        <v>2.942671347120522</v>
+        <v>3.011201187528545</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.181778132028255</v>
+        <v>2.146588162156831</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1113553193929513</v>
+        <v>0.111292137974629</v>
       </c>
       <c r="C64">
-        <v>11.7504006991144</v>
+        <v>11.5340687174514</v>
       </c>
       <c r="D64">
-        <v>25.4834006991144</v>
+        <v>25.4940687174514</v>
       </c>
       <c r="E64">
-        <v>1.174000000000001</v>
+        <v>1.401000000000002</v>
       </c>
       <c r="F64">
-        <v>14.074</v>
+        <v>14.301</v>
       </c>
       <c r="G64">
         <v>0.341</v>
@@ -6523,28 +6523,28 @@
         <v>2.29</v>
       </c>
       <c r="M64">
-        <v>1.0668092</v>
+        <v>1.0840158</v>
       </c>
       <c r="N64">
-        <v>1.2231908</v>
+        <v>1.2059842</v>
       </c>
       <c r="O64">
-        <v>0.3057977</v>
+        <v>0.30149605</v>
       </c>
       <c r="P64">
-        <v>0.9173930999999999</v>
+        <v>0.9044881499999999</v>
       </c>
       <c r="Q64">
-        <v>3.2473931</v>
+        <v>3.23448815</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2002850510340824</v>
+        <v>0.2039909134449432</v>
       </c>
       <c r="T64">
-        <v>3.011201187528545</v>
+        <v>3.083435343634299</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.146588162156831</v>
+        <v>2.112515334186088</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.111292137974629</v>
+        <v>0.1112289565563066</v>
       </c>
       <c r="C65">
-        <v>11.5340687174514</v>
+        <v>11.3177456713523</v>
       </c>
       <c r="D65">
-        <v>25.4940687174514</v>
+        <v>25.5047456713523</v>
       </c>
       <c r="E65">
-        <v>1.401000000000002</v>
+        <v>1.628000000000002</v>
       </c>
       <c r="F65">
-        <v>14.301</v>
+        <v>14.528</v>
       </c>
       <c r="G65">
         <v>0.341</v>
@@ -6605,28 +6605,28 @@
         <v>2.29</v>
       </c>
       <c r="M65">
-        <v>1.0840158</v>
+        <v>1.1012224</v>
       </c>
       <c r="N65">
-        <v>1.2059842</v>
+        <v>1.1887776</v>
       </c>
       <c r="O65">
-        <v>0.30149605</v>
+        <v>0.2971944</v>
       </c>
       <c r="P65">
-        <v>0.9044881499999999</v>
+        <v>0.8915831999999999</v>
       </c>
       <c r="Q65">
-        <v>3.23448815</v>
+        <v>3.2215832</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2039909134449432</v>
+        <v>0.2079026571008518</v>
       </c>
       <c r="T65">
-        <v>3.083435343634299</v>
+        <v>3.159682508412596</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.112515334186088</v>
+        <v>2.07950728208943</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1112289565563066</v>
+        <v>0.1111657751379843</v>
       </c>
       <c r="C66">
-        <v>11.3177456713523</v>
+        <v>11.10143157204847</v>
       </c>
       <c r="D66">
-        <v>25.5047456713523</v>
+        <v>25.51543157204847</v>
       </c>
       <c r="E66">
-        <v>1.628000000000002</v>
+        <v>1.855000000000002</v>
       </c>
       <c r="F66">
-        <v>14.528</v>
+        <v>14.755</v>
       </c>
       <c r="G66">
         <v>0.341</v>
@@ -6687,28 +6687,28 @@
         <v>2.29</v>
       </c>
       <c r="M66">
-        <v>1.1012224</v>
+        <v>1.118429</v>
       </c>
       <c r="N66">
-        <v>1.1887776</v>
+        <v>1.171571</v>
       </c>
       <c r="O66">
-        <v>0.2971944</v>
+        <v>0.2928927499999999</v>
       </c>
       <c r="P66">
-        <v>0.8915831999999999</v>
+        <v>0.8786782499999998</v>
       </c>
       <c r="Q66">
-        <v>3.2215832</v>
+        <v>3.20867825</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2079026571008518</v>
+        <v>0.2120379289656694</v>
       </c>
       <c r="T66">
-        <v>3.159682508412596</v>
+        <v>3.240286654035366</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.07950728208943</v>
+        <v>2.047514862364977</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1111657751379843</v>
+        <v>0.1111025937196619</v>
       </c>
       <c r="C67">
-        <v>11.10143157204847</v>
+        <v>10.88512643079015</v>
       </c>
       <c r="D67">
-        <v>25.51543157204847</v>
+        <v>25.52612643079015</v>
       </c>
       <c r="E67">
-        <v>1.855000000000002</v>
+        <v>2.082000000000003</v>
       </c>
       <c r="F67">
-        <v>14.755</v>
+        <v>14.982</v>
       </c>
       <c r="G67">
         <v>0.341</v>
@@ -6769,28 +6769,28 @@
         <v>2.29</v>
       </c>
       <c r="M67">
-        <v>1.118429</v>
+        <v>1.1356356</v>
       </c>
       <c r="N67">
-        <v>1.171571</v>
+        <v>1.1543644</v>
       </c>
       <c r="O67">
-        <v>0.2928927499999999</v>
+        <v>0.2885910999999999</v>
       </c>
       <c r="P67">
-        <v>0.8786782499999998</v>
+        <v>0.8657732999999999</v>
       </c>
       <c r="Q67">
-        <v>3.20867825</v>
+        <v>3.1957733</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2120379289656694</v>
+        <v>0.2164164521166528</v>
       </c>
       <c r="T67">
-        <v>3.240286654035366</v>
+        <v>3.325632219988887</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.047514862364977</v>
+        <v>2.016491909904902</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1111025937196619</v>
+        <v>0.1181749123013396</v>
       </c>
       <c r="C68">
-        <v>10.88512643079015</v>
+        <v>9.514151255237667</v>
       </c>
       <c r="D68">
-        <v>25.52612643079015</v>
+        <v>24.38215125523767</v>
       </c>
       <c r="E68">
-        <v>2.082000000000003</v>
+        <v>2.309000000000003</v>
       </c>
       <c r="F68">
-        <v>14.982</v>
+        <v>15.209</v>
       </c>
       <c r="G68">
         <v>0.341</v>
@@ -6851,45 +6851,45 @@
         <v>2.29</v>
       </c>
       <c r="M68">
-        <v>1.1356356</v>
+        <v>1.36881</v>
       </c>
       <c r="N68">
-        <v>1.1543644</v>
+        <v>0.9211899999999997</v>
       </c>
       <c r="O68">
-        <v>0.2885910999999999</v>
+        <v>0.2302974999999999</v>
       </c>
       <c r="P68">
-        <v>0.8657732999999999</v>
+        <v>0.6908924999999998</v>
       </c>
       <c r="Q68">
-        <v>3.1957733</v>
+        <v>3.0208925</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2164164521166528</v>
+        <v>0.2210603403070897</v>
       </c>
       <c r="T68">
-        <v>3.325632219988887</v>
+        <v>3.416150244485046</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.016491909904902</v>
+        <v>1.672986024356923</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1181749123013396</v>
+        <v>0.1182182308830173</v>
       </c>
       <c r="C69">
-        <v>9.514151255237667</v>
+        <v>9.280460164485135</v>
       </c>
       <c r="D69">
-        <v>24.38215125523767</v>
+        <v>24.37546016448514</v>
       </c>
       <c r="E69">
-        <v>2.309000000000003</v>
+        <v>2.536000000000003</v>
       </c>
       <c r="F69">
-        <v>15.209</v>
+        <v>15.436</v>
       </c>
       <c r="G69">
         <v>0.341</v>
@@ -6933,28 +6933,28 @@
         <v>2.29</v>
       </c>
       <c r="M69">
-        <v>1.36881</v>
+        <v>1.38924</v>
       </c>
       <c r="N69">
-        <v>0.9211899999999997</v>
+        <v>0.9007599999999998</v>
       </c>
       <c r="O69">
-        <v>0.2302974999999999</v>
+        <v>0.2251899999999999</v>
       </c>
       <c r="P69">
-        <v>0.6908924999999998</v>
+        <v>0.6755699999999998</v>
       </c>
       <c r="Q69">
-        <v>3.0208925</v>
+        <v>3.00557</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2210603403070897</v>
+        <v>0.225994471509429</v>
       </c>
       <c r="T69">
-        <v>3.416150244485046</v>
+        <v>3.512325645512216</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.672986024356923</v>
+        <v>1.648383288704615</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1182182308830173</v>
+        <v>0.1182615494646949</v>
       </c>
       <c r="C70">
-        <v>9.280460164485135</v>
+        <v>9.04677274514059</v>
       </c>
       <c r="D70">
-        <v>24.37546016448514</v>
+        <v>24.36877274514059</v>
       </c>
       <c r="E70">
-        <v>2.536000000000003</v>
+        <v>2.763000000000003</v>
       </c>
       <c r="F70">
-        <v>15.436</v>
+        <v>15.663</v>
       </c>
       <c r="G70">
         <v>0.341</v>
@@ -7015,28 +7015,28 @@
         <v>2.29</v>
       </c>
       <c r="M70">
-        <v>1.38924</v>
+        <v>1.40967</v>
       </c>
       <c r="N70">
-        <v>0.9007599999999998</v>
+        <v>0.8803299999999998</v>
       </c>
       <c r="O70">
-        <v>0.2251899999999999</v>
+        <v>0.2200825</v>
       </c>
       <c r="P70">
-        <v>0.6755699999999998</v>
+        <v>0.6602474999999999</v>
       </c>
       <c r="Q70">
-        <v>3.00557</v>
+        <v>2.9902475</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.225994471509429</v>
+        <v>0.2312469337570804</v>
       </c>
       <c r="T70">
-        <v>3.512325645512216</v>
+        <v>3.614705911121783</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.648383288704615</v>
+        <v>1.624493675824838</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1182615494646949</v>
+        <v>0.1183048680463726</v>
       </c>
       <c r="C71">
-        <v>9.04677274514059</v>
+        <v>8.813088994183129</v>
       </c>
       <c r="D71">
-        <v>24.36877274514059</v>
+        <v>24.36208899418313</v>
       </c>
       <c r="E71">
-        <v>2.763000000000003</v>
+        <v>2.990000000000004</v>
       </c>
       <c r="F71">
-        <v>15.663</v>
+        <v>15.89</v>
       </c>
       <c r="G71">
         <v>0.341</v>
@@ -7097,28 +7097,28 @@
         <v>2.29</v>
       </c>
       <c r="M71">
-        <v>1.40967</v>
+        <v>1.4301</v>
       </c>
       <c r="N71">
-        <v>0.8803299999999998</v>
+        <v>0.8598999999999997</v>
       </c>
       <c r="O71">
-        <v>0.2200825</v>
+        <v>0.2149749999999999</v>
       </c>
       <c r="P71">
-        <v>0.6602474999999999</v>
+        <v>0.6449249999999997</v>
       </c>
       <c r="Q71">
-        <v>2.9902475</v>
+        <v>2.974925</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2312469337570804</v>
+        <v>0.2368495601545753</v>
       </c>
       <c r="T71">
-        <v>3.614705911121783</v>
+        <v>3.723911527771988</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.624493675824838</v>
+        <v>1.601286623313054</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1183048680463726</v>
+        <v>0.1183481866280502</v>
       </c>
       <c r="C72">
-        <v>8.813088994183129</v>
+        <v>8.57940890859512</v>
       </c>
       <c r="D72">
-        <v>24.36208899418313</v>
+        <v>24.35540890859512</v>
       </c>
       <c r="E72">
-        <v>2.990000000000004</v>
+        <v>3.217000000000004</v>
       </c>
       <c r="F72">
-        <v>15.89</v>
+        <v>16.117</v>
       </c>
       <c r="G72">
         <v>0.341</v>
@@ -7179,28 +7179,28 @@
         <v>2.29</v>
       </c>
       <c r="M72">
-        <v>1.4301</v>
+        <v>1.45053</v>
       </c>
       <c r="N72">
-        <v>0.8598999999999997</v>
+        <v>0.8394699999999997</v>
       </c>
       <c r="O72">
-        <v>0.2149749999999999</v>
+        <v>0.2098674999999999</v>
       </c>
       <c r="P72">
-        <v>0.6449249999999997</v>
+        <v>0.6296024999999998</v>
       </c>
       <c r="Q72">
-        <v>2.974925</v>
+        <v>2.9596025</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2368495601545753</v>
+        <v>0.2428385745794836</v>
       </c>
       <c r="T72">
-        <v>3.723911527771988</v>
+        <v>3.840648566260139</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.601286623313054</v>
+        <v>1.578733290590336</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1183481866280502</v>
+        <v>0.1183915052097279</v>
       </c>
       <c r="C73">
-        <v>8.579408908595124</v>
+        <v>8.345732485362262</v>
       </c>
       <c r="D73">
-        <v>24.35540890859512</v>
+        <v>24.34873248536226</v>
       </c>
       <c r="E73">
-        <v>3.217000000000001</v>
+        <v>3.444000000000001</v>
       </c>
       <c r="F73">
-        <v>16.117</v>
+        <v>16.344</v>
       </c>
       <c r="G73">
         <v>0.341</v>
@@ -7261,28 +7261,28 @@
         <v>2.29</v>
       </c>
       <c r="M73">
-        <v>1.45053</v>
+        <v>1.47096</v>
       </c>
       <c r="N73">
-        <v>0.8394699999999999</v>
+        <v>0.81904</v>
       </c>
       <c r="O73">
-        <v>0.2098675</v>
+        <v>0.20476</v>
       </c>
       <c r="P73">
-        <v>0.6296025</v>
+        <v>0.6142799999999999</v>
       </c>
       <c r="Q73">
-        <v>2.9596025</v>
+        <v>2.94428</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2428385745794836</v>
+        <v>0.2492553757490282</v>
       </c>
       <c r="T73">
-        <v>3.840648566260138</v>
+        <v>3.965723964640298</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.578733290590336</v>
+        <v>1.556806439332137</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1183915052097279</v>
+        <v>0.1184348237914055</v>
       </c>
       <c r="C74">
-        <v>8.345732485362262</v>
+        <v>8.112059721473553</v>
       </c>
       <c r="D74">
-        <v>24.34873248536226</v>
+        <v>24.34205972147355</v>
       </c>
       <c r="E74">
-        <v>3.444000000000001</v>
+        <v>3.671000000000001</v>
       </c>
       <c r="F74">
-        <v>16.344</v>
+        <v>16.571</v>
       </c>
       <c r="G74">
         <v>0.341</v>
@@ -7343,28 +7343,28 @@
         <v>2.29</v>
       </c>
       <c r="M74">
-        <v>1.47096</v>
+        <v>1.49139</v>
       </c>
       <c r="N74">
-        <v>0.81904</v>
+        <v>0.79861</v>
       </c>
       <c r="O74">
-        <v>0.20476</v>
+        <v>0.1996525</v>
       </c>
       <c r="P74">
-        <v>0.6142799999999999</v>
+        <v>0.5989575</v>
       </c>
       <c r="Q74">
-        <v>2.94428</v>
+        <v>2.9289575</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2492553757490282</v>
+        <v>0.2561474955237242</v>
       </c>
       <c r="T74">
-        <v>3.965723964640298</v>
+        <v>4.100064207344915</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.556806439332137</v>
+        <v>1.535480323724847</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1184348237914055</v>
+        <v>0.1184781423730832</v>
       </c>
       <c r="C75">
-        <v>8.112059721473553</v>
+        <v>7.878390613921283</v>
       </c>
       <c r="D75">
-        <v>24.34205972147355</v>
+        <v>24.33539061392128</v>
       </c>
       <c r="E75">
-        <v>3.671000000000001</v>
+        <v>3.898000000000001</v>
       </c>
       <c r="F75">
-        <v>16.571</v>
+        <v>16.798</v>
       </c>
       <c r="G75">
         <v>0.341</v>
@@ -7425,28 +7425,28 @@
         <v>2.29</v>
       </c>
       <c r="M75">
-        <v>1.49139</v>
+        <v>1.51182</v>
       </c>
       <c r="N75">
-        <v>0.79861</v>
+        <v>0.7781799999999999</v>
       </c>
       <c r="O75">
-        <v>0.1996525</v>
+        <v>0.194545</v>
       </c>
       <c r="P75">
-        <v>0.5989575</v>
+        <v>0.5836349999999999</v>
       </c>
       <c r="Q75">
-        <v>2.9289575</v>
+        <v>2.913635</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2561474955237242</v>
+        <v>0.2635697783580123</v>
       </c>
       <c r="T75">
-        <v>4.100064207344915</v>
+        <v>4.244738314872964</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.535480323724847</v>
+        <v>1.514730589620457</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1184781423730832</v>
+        <v>0.1538669044366271</v>
       </c>
       <c r="C76">
-        <v>7.878390613921283</v>
+        <v>3.200757131432606</v>
       </c>
       <c r="D76">
-        <v>24.33539061392128</v>
+        <v>19.88475713143261</v>
       </c>
       <c r="E76">
-        <v>3.898000000000001</v>
+        <v>4.125000000000002</v>
       </c>
       <c r="F76">
-        <v>16.798</v>
+        <v>17.025</v>
       </c>
       <c r="G76">
         <v>0.341</v>
@@ -7507,45 +7507,45 @@
         <v>2.29</v>
       </c>
       <c r="M76">
-        <v>1.51182</v>
+        <v>2.499270000000001</v>
       </c>
       <c r="N76">
-        <v>0.7781799999999999</v>
+        <v>-0.2092700000000005</v>
       </c>
       <c r="O76">
-        <v>0.194545</v>
+        <v>-0.05231750000000013</v>
       </c>
       <c r="P76">
-        <v>0.5836349999999999</v>
+        <v>-0.1569525000000004</v>
       </c>
       <c r="Q76">
-        <v>2.913635</v>
+        <v>2.1730475</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2635697783580123</v>
+        <v>0.2759486750152308</v>
       </c>
       <c r="T76">
-        <v>4.244738314872964</v>
+        <v>4.486026051550383</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.25</v>
+        <v>0.2290668875311591</v>
       </c>
       <c r="W76">
-        <v>0.0675</v>
+        <v>0.1131729809104259</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.514730589620457</v>
+        <v>0.9162675501246362</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1538669044366271</v>
+        <v>0.1548769044366271</v>
       </c>
       <c r="C77">
-        <v>3.200757131432606</v>
+        <v>2.870505043333932</v>
       </c>
       <c r="D77">
-        <v>19.88475713143261</v>
+        <v>19.78150504333393</v>
       </c>
       <c r="E77">
-        <v>4.125000000000002</v>
+        <v>4.352000000000002</v>
       </c>
       <c r="F77">
-        <v>17.025</v>
+        <v>17.252</v>
       </c>
       <c r="G77">
         <v>0.341</v>
@@ -7589,37 +7589,37 @@
         <v>2.29</v>
       </c>
       <c r="M77">
-        <v>2.499270000000001</v>
+        <v>2.532593600000001</v>
       </c>
       <c r="N77">
-        <v>-0.2092700000000005</v>
+        <v>-0.2425936000000006</v>
       </c>
       <c r="O77">
-        <v>-0.05231750000000013</v>
+        <v>-0.06064840000000016</v>
       </c>
       <c r="P77">
-        <v>-0.1569525000000004</v>
+        <v>-0.1819452000000005</v>
       </c>
       <c r="Q77">
-        <v>2.1730475</v>
+        <v>2.1480548</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2759486750152308</v>
+        <v>0.2855382031408654</v>
       </c>
       <c r="T77">
-        <v>4.486026051550383</v>
+        <v>4.672943803698316</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2290668875311591</v>
+        <v>0.226052849537328</v>
       </c>
       <c r="W77">
-        <v>0.1131729809104259</v>
+        <v>0.1136154416879203</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9162675501246362</v>
+        <v>0.9042113981493121</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1548769044366271</v>
+        <v>0.1558869044366271</v>
       </c>
       <c r="C78">
-        <v>2.870505043333932</v>
+        <v>2.541319694156545</v>
       </c>
       <c r="D78">
-        <v>19.78150504333393</v>
+        <v>19.67931969415655</v>
       </c>
       <c r="E78">
-        <v>4.352000000000002</v>
+        <v>4.579000000000002</v>
       </c>
       <c r="F78">
-        <v>17.252</v>
+        <v>17.479</v>
       </c>
       <c r="G78">
         <v>0.341</v>
@@ -7671,37 +7671,37 @@
         <v>2.29</v>
       </c>
       <c r="M78">
-        <v>2.532593600000001</v>
+        <v>2.565917200000001</v>
       </c>
       <c r="N78">
-        <v>-0.2425936000000006</v>
+        <v>-0.2759172000000008</v>
       </c>
       <c r="O78">
-        <v>-0.06064840000000016</v>
+        <v>-0.06897930000000019</v>
       </c>
       <c r="P78">
-        <v>-0.1819452000000005</v>
+        <v>-0.2069379000000006</v>
       </c>
       <c r="Q78">
-        <v>2.1480548</v>
+        <v>2.123062099999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2855382031408654</v>
+        <v>0.2959616032774247</v>
       </c>
       <c r="T78">
-        <v>4.672943803698316</v>
+        <v>4.876115273424329</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.226052849537328</v>
+        <v>0.2231170982446354</v>
       </c>
       <c r="W78">
-        <v>0.1136154416879203</v>
+        <v>0.1140464099776875</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9042113981493121</v>
+        <v>0.8924683929785416</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1558869044366271</v>
+        <v>0.1568969044366271</v>
       </c>
       <c r="C79">
-        <v>2.541319694156545</v>
+        <v>2.21318463749331</v>
       </c>
       <c r="D79">
-        <v>19.67931969415655</v>
+        <v>19.57818463749331</v>
       </c>
       <c r="E79">
-        <v>4.579000000000002</v>
+        <v>4.806000000000003</v>
       </c>
       <c r="F79">
-        <v>17.479</v>
+        <v>17.706</v>
       </c>
       <c r="G79">
         <v>0.341</v>
@@ -7753,37 +7753,37 @@
         <v>2.29</v>
       </c>
       <c r="M79">
-        <v>2.565917200000001</v>
+        <v>2.599240800000001</v>
       </c>
       <c r="N79">
-        <v>-0.2759172000000008</v>
+        <v>-0.3092408000000009</v>
       </c>
       <c r="O79">
-        <v>-0.06897930000000019</v>
+        <v>-0.07731020000000022</v>
       </c>
       <c r="P79">
-        <v>-0.2069379000000006</v>
+        <v>-0.2319306000000007</v>
       </c>
       <c r="Q79">
-        <v>2.123062099999999</v>
+        <v>2.0980694</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2959616032774247</v>
+        <v>0.3073325852445805</v>
       </c>
       <c r="T79">
-        <v>4.876115273424329</v>
+        <v>5.0977568767618</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2231170982446354</v>
+        <v>0.2202566226261145</v>
       </c>
       <c r="W79">
-        <v>0.1140464099776875</v>
+        <v>0.1144663277984864</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8924683929785416</v>
+        <v>0.8810264905044578</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1568969044366271</v>
+        <v>0.1579069044366271</v>
       </c>
       <c r="C80">
-        <v>2.21318463749331</v>
+        <v>1.886083763291012</v>
       </c>
       <c r="D80">
-        <v>19.57818463749331</v>
+        <v>19.47808376329101</v>
       </c>
       <c r="E80">
-        <v>4.806000000000003</v>
+        <v>5.033000000000003</v>
       </c>
       <c r="F80">
-        <v>17.706</v>
+        <v>17.933</v>
       </c>
       <c r="G80">
         <v>0.341</v>
@@ -7835,37 +7835,37 @@
         <v>2.29</v>
       </c>
       <c r="M80">
-        <v>2.599240800000001</v>
+        <v>2.632564400000001</v>
       </c>
       <c r="N80">
-        <v>-0.3092408000000009</v>
+        <v>-0.3425644000000005</v>
       </c>
       <c r="O80">
-        <v>-0.07731020000000022</v>
+        <v>-0.08564110000000014</v>
       </c>
       <c r="P80">
-        <v>-0.2319306000000007</v>
+        <v>-0.2569233000000004</v>
       </c>
       <c r="Q80">
-        <v>2.0980694</v>
+        <v>2.0730767</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3073325852445805</v>
+        <v>0.3197865178752747</v>
       </c>
       <c r="T80">
-        <v>5.0977568767618</v>
+        <v>5.340507204226647</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2202566226261145</v>
+        <v>0.2174685641118599</v>
       </c>
       <c r="W80">
-        <v>0.1144663277984864</v>
+        <v>0.114875614788379</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8810264905044578</v>
+        <v>0.8698742564474394</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1579069044366271</v>
+        <v>0.1589169044366271</v>
       </c>
       <c r="C81">
-        <v>1.886083763291012</v>
+        <v>1.560001289295382</v>
       </c>
       <c r="D81">
-        <v>19.47808376329101</v>
+        <v>19.37900128929538</v>
       </c>
       <c r="E81">
-        <v>5.033000000000003</v>
+        <v>5.260000000000003</v>
       </c>
       <c r="F81">
-        <v>17.933</v>
+        <v>18.16</v>
       </c>
       <c r="G81">
         <v>0.341</v>
@@ -7917,37 +7917,37 @@
         <v>2.29</v>
       </c>
       <c r="M81">
-        <v>2.632564400000001</v>
+        <v>2.665888000000001</v>
       </c>
       <c r="N81">
-        <v>-0.3425644000000005</v>
+        <v>-0.3758880000000007</v>
       </c>
       <c r="O81">
-        <v>-0.08564110000000014</v>
+        <v>-0.09397200000000017</v>
       </c>
       <c r="P81">
-        <v>-0.2569233000000004</v>
+        <v>-0.2819160000000005</v>
       </c>
       <c r="Q81">
-        <v>2.0730767</v>
+        <v>2.048083999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3197865178752747</v>
+        <v>0.3334858437690385</v>
       </c>
       <c r="T81">
-        <v>5.340507204226647</v>
+        <v>5.607532564437979</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2174685641118599</v>
+        <v>0.2147502070604616</v>
       </c>
       <c r="W81">
-        <v>0.114875614788379</v>
+        <v>0.1152746696035242</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8698742564474394</v>
+        <v>0.8590008282418464</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1589169044366271</v>
+        <v>0.1599269044366271</v>
       </c>
       <c r="C82">
-        <v>1.560001289295382</v>
+        <v>1.234921752755984</v>
       </c>
       <c r="D82">
-        <v>19.37900128929538</v>
+        <v>19.28092175275599</v>
       </c>
       <c r="E82">
-        <v>5.260000000000003</v>
+        <v>5.487000000000004</v>
       </c>
       <c r="F82">
-        <v>18.16</v>
+        <v>18.387</v>
       </c>
       <c r="G82">
         <v>0.341</v>
@@ -7999,37 +7999,37 @@
         <v>2.29</v>
       </c>
       <c r="M82">
-        <v>2.665888000000001</v>
+        <v>2.699211600000001</v>
       </c>
       <c r="N82">
-        <v>-0.3758880000000007</v>
+        <v>-0.4092116000000008</v>
       </c>
       <c r="O82">
-        <v>-0.09397200000000017</v>
+        <v>-0.1023029000000002</v>
       </c>
       <c r="P82">
-        <v>-0.2819160000000005</v>
+        <v>-0.3069087000000006</v>
       </c>
       <c r="Q82">
-        <v>2.048083999999999</v>
+        <v>2.023091299999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3334858437690385</v>
+        <v>0.348627203967409</v>
       </c>
       <c r="T82">
-        <v>5.607532564437979</v>
+        <v>5.902665857303137</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2147502070604616</v>
+        <v>0.2120989699362584</v>
       </c>
       <c r="W82">
-        <v>0.1152746696035242</v>
+        <v>0.1156638712133573</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8590008282418464</v>
+        <v>0.8483958797450335</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1599269044366271</v>
+        <v>0.1609369044366271</v>
       </c>
       <c r="C83">
-        <v>1.234921752755984</v>
+        <v>0.9108300023816511</v>
       </c>
       <c r="D83">
-        <v>19.28092175275599</v>
+        <v>19.18383000238165</v>
       </c>
       <c r="E83">
-        <v>5.487000000000004</v>
+        <v>5.714000000000004</v>
       </c>
       <c r="F83">
-        <v>18.387</v>
+        <v>18.614</v>
       </c>
       <c r="G83">
         <v>0.341</v>
@@ -8081,37 +8081,37 @@
         <v>2.29</v>
       </c>
       <c r="M83">
-        <v>2.699211600000001</v>
+        <v>2.732535200000001</v>
       </c>
       <c r="N83">
-        <v>-0.4092116000000008</v>
+        <v>-0.4425352000000009</v>
       </c>
       <c r="O83">
-        <v>-0.1023029000000002</v>
+        <v>-0.1106338000000002</v>
       </c>
       <c r="P83">
-        <v>-0.3069087000000006</v>
+        <v>-0.3319014000000007</v>
       </c>
       <c r="Q83">
-        <v>2.023091299999999</v>
+        <v>1.998098599999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.348627203967409</v>
+        <v>0.3654509375211539</v>
       </c>
       <c r="T83">
-        <v>5.902665857303137</v>
+        <v>6.230591738264422</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2120989699362584</v>
+        <v>0.2095123971321576</v>
       </c>
       <c r="W83">
-        <v>0.1156638712133573</v>
+        <v>0.1160435801009993</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8483958797450335</v>
+        <v>0.8380495885286305</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1609369044366271</v>
+        <v>0.1619469044366271</v>
       </c>
       <c r="C84">
-        <v>0.9108300023816511</v>
+        <v>0.5877111905377994</v>
       </c>
       <c r="D84">
-        <v>19.18383000238165</v>
+        <v>19.0877111905378</v>
       </c>
       <c r="E84">
-        <v>5.714000000000004</v>
+        <v>5.941000000000004</v>
       </c>
       <c r="F84">
-        <v>18.614</v>
+        <v>18.841</v>
       </c>
       <c r="G84">
         <v>0.341</v>
@@ -8163,37 +8163,37 @@
         <v>2.29</v>
       </c>
       <c r="M84">
-        <v>2.732535200000001</v>
+        <v>2.765858800000001</v>
       </c>
       <c r="N84">
-        <v>-0.4425352000000009</v>
+        <v>-0.475858800000001</v>
       </c>
       <c r="O84">
-        <v>-0.1106338000000002</v>
+        <v>-0.1189647000000003</v>
       </c>
       <c r="P84">
-        <v>-0.3319014000000007</v>
+        <v>-0.3568941000000008</v>
       </c>
       <c r="Q84">
-        <v>1.998098599999999</v>
+        <v>1.973105899999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3654509375211539</v>
+        <v>0.3842539338459277</v>
       </c>
       <c r="T84">
-        <v>6.230591738264422</v>
+        <v>6.597097134632918</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2095123971321576</v>
+        <v>0.2069881513835774</v>
       </c>
       <c r="W84">
-        <v>0.1160435801009993</v>
+        <v>0.1164141393768909</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8380495885286305</v>
+        <v>0.8279526055343097</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1619469044366271</v>
+        <v>0.1629569044366271</v>
       </c>
       <c r="C85">
-        <v>0.5877111905377994</v>
+        <v>0.2655507656771654</v>
       </c>
       <c r="D85">
-        <v>19.0877111905378</v>
+        <v>18.99255076567717</v>
       </c>
       <c r="E85">
-        <v>5.941000000000004</v>
+        <v>6.168000000000005</v>
       </c>
       <c r="F85">
-        <v>18.841</v>
+        <v>19.068</v>
       </c>
       <c r="G85">
         <v>0.341</v>
@@ -8245,37 +8245,37 @@
         <v>2.29</v>
       </c>
       <c r="M85">
-        <v>2.765858800000001</v>
+        <v>2.799182400000001</v>
       </c>
       <c r="N85">
-        <v>-0.475858800000001</v>
+        <v>-0.5091824000000011</v>
       </c>
       <c r="O85">
-        <v>-0.1189647000000003</v>
+        <v>-0.1272956000000003</v>
       </c>
       <c r="P85">
-        <v>-0.3568941000000008</v>
+        <v>-0.3818868000000009</v>
       </c>
       <c r="Q85">
-        <v>1.973105899999999</v>
+        <v>1.948113199999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3842539338459277</v>
+        <v>0.4054073047112983</v>
       </c>
       <c r="T85">
-        <v>6.597097134632918</v>
+        <v>7.009415705547477</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2069881513835774</v>
+        <v>0.2045240067242491</v>
       </c>
       <c r="W85">
-        <v>0.1164141393768909</v>
+        <v>0.1167758758128803</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8279526055343097</v>
+        <v>0.8180960268969965</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1629569044366271</v>
+        <v>0.1639669044366271</v>
       </c>
       <c r="C86">
-        <v>0.2655507656771725</v>
+        <v>-0.05566553500423055</v>
       </c>
       <c r="D86">
-        <v>18.99255076567717</v>
+        <v>18.89833446499577</v>
       </c>
       <c r="E86">
-        <v>6.168000000000001</v>
+        <v>6.395000000000001</v>
       </c>
       <c r="F86">
-        <v>19.068</v>
+        <v>19.295</v>
       </c>
       <c r="G86">
         <v>0.341</v>
@@ -8327,37 +8327,37 @@
         <v>2.29</v>
       </c>
       <c r="M86">
-        <v>2.7991824</v>
+        <v>2.832506</v>
       </c>
       <c r="N86">
-        <v>-0.5091824000000003</v>
+        <v>-0.5425060000000004</v>
       </c>
       <c r="O86">
-        <v>-0.1272956000000001</v>
+        <v>-0.1356265000000001</v>
       </c>
       <c r="P86">
-        <v>-0.3818868000000002</v>
+        <v>-0.4068795000000003</v>
       </c>
       <c r="Q86">
-        <v>1.9481132</v>
+        <v>1.9231205</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4054073047112979</v>
+        <v>0.4293811250253846</v>
       </c>
       <c r="T86">
-        <v>7.009415705547471</v>
+        <v>7.476710085917303</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2045240067242492</v>
+        <v>0.202117841939258</v>
       </c>
       <c r="W86">
-        <v>0.1167758758128802</v>
+        <v>0.1171291008033169</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8180960268969967</v>
+        <v>0.808471367757032</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1639669044366271</v>
+        <v>0.2146266231769506</v>
       </c>
       <c r="C87">
-        <v>-0.05566553500423055</v>
+        <v>-4.04803905354534</v>
       </c>
       <c r="D87">
-        <v>18.89833446499577</v>
+        <v>15.13296094645466</v>
       </c>
       <c r="E87">
-        <v>6.395000000000001</v>
+        <v>6.622000000000002</v>
       </c>
       <c r="F87">
-        <v>19.295</v>
+        <v>19.522</v>
       </c>
       <c r="G87">
         <v>0.341</v>
@@ -8409,45 +8409,45 @@
         <v>2.29</v>
       </c>
       <c r="M87">
-        <v>2.832506</v>
+        <v>3.9200176</v>
       </c>
       <c r="N87">
-        <v>-0.5425060000000004</v>
+        <v>-1.6300176</v>
       </c>
       <c r="O87">
-        <v>-0.1356265000000001</v>
+        <v>-0.4075044000000001</v>
       </c>
       <c r="P87">
-        <v>-0.4068795000000003</v>
+        <v>-1.2225132</v>
       </c>
       <c r="Q87">
-        <v>1.9231205</v>
+        <v>1.1074868</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4293811250253846</v>
+        <v>0.4797063392437939</v>
       </c>
       <c r="T87">
-        <v>7.476710085917303</v>
+        <v>8.457642181306069</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.202117841939258</v>
+        <v>0.1460452626539228</v>
       </c>
       <c r="W87">
-        <v>0.1171291008033169</v>
+        <v>0.1714741112590923</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.808471367757032</v>
+        <v>0.584181050615691</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2146266231769506</v>
+        <v>0.2161766231769505</v>
       </c>
       <c r="C88">
-        <v>-4.04803905354534</v>
+        <v>-4.366732415044165</v>
       </c>
       <c r="D88">
-        <v>15.13296094645466</v>
+        <v>15.04126758495584</v>
       </c>
       <c r="E88">
-        <v>6.622000000000002</v>
+        <v>6.849000000000002</v>
       </c>
       <c r="F88">
-        <v>19.522</v>
+        <v>19.749</v>
       </c>
       <c r="G88">
         <v>0.341</v>
@@ -8491,37 +8491,37 @@
         <v>2.29</v>
       </c>
       <c r="M88">
-        <v>3.9200176</v>
+        <v>3.965599200000001</v>
       </c>
       <c r="N88">
-        <v>-1.6300176</v>
+        <v>-1.675599200000001</v>
       </c>
       <c r="O88">
-        <v>-0.4075044000000001</v>
+        <v>-0.4188998000000002</v>
       </c>
       <c r="P88">
-        <v>-1.2225132</v>
+        <v>-1.2566994</v>
       </c>
       <c r="Q88">
-        <v>1.1074868</v>
+        <v>1.0733006</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4797063392437939</v>
+        <v>0.513083749954855</v>
       </c>
       <c r="T88">
-        <v>8.457642181306069</v>
+        <v>9.108230041406536</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1460452626539228</v>
+        <v>0.1443665814739926</v>
       </c>
       <c r="W88">
-        <v>0.1714741112590923</v>
+        <v>0.1718111904400223</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.584181050615691</v>
+        <v>0.5774663258959705</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2161766231769505</v>
+        <v>0.2177266231769505</v>
       </c>
       <c r="C89">
-        <v>-4.366732415044165</v>
+        <v>-4.684321295301851</v>
       </c>
       <c r="D89">
-        <v>15.04126758495584</v>
+        <v>14.95067870469815</v>
       </c>
       <c r="E89">
-        <v>6.849000000000002</v>
+        <v>7.076000000000002</v>
       </c>
       <c r="F89">
-        <v>19.749</v>
+        <v>19.976</v>
       </c>
       <c r="G89">
         <v>0.341</v>
@@ -8573,37 +8573,37 @@
         <v>2.29</v>
       </c>
       <c r="M89">
-        <v>3.965599200000001</v>
+        <v>4.011180800000001</v>
       </c>
       <c r="N89">
-        <v>-1.675599200000001</v>
+        <v>-1.721180800000001</v>
       </c>
       <c r="O89">
-        <v>-0.4188998000000002</v>
+        <v>-0.4302952000000002</v>
       </c>
       <c r="P89">
-        <v>-1.2566994</v>
+        <v>-1.290885600000001</v>
       </c>
       <c r="Q89">
-        <v>1.0733006</v>
+        <v>1.039114399999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.513083749954855</v>
+        <v>0.5520240624510929</v>
       </c>
       <c r="T89">
-        <v>9.108230041406536</v>
+        <v>9.867249211523749</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1443665814739926</v>
+        <v>0.1427260521390609</v>
       </c>
       <c r="W89">
-        <v>0.1718111904400223</v>
+        <v>0.1721406087304766</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5774663258959705</v>
+        <v>0.5709042085562435</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2177266231769505</v>
+        <v>0.2192766231769506</v>
       </c>
       <c r="C90">
-        <v>-4.684321295301851</v>
+        <v>-5.000825530691914</v>
       </c>
       <c r="D90">
-        <v>14.95067870469815</v>
+        <v>14.86117446930809</v>
       </c>
       <c r="E90">
-        <v>7.076000000000002</v>
+        <v>7.303000000000003</v>
       </c>
       <c r="F90">
-        <v>19.976</v>
+        <v>20.203</v>
       </c>
       <c r="G90">
         <v>0.341</v>
@@ -8655,37 +8655,37 @@
         <v>2.29</v>
       </c>
       <c r="M90">
-        <v>4.011180800000001</v>
+        <v>4.056762400000001</v>
       </c>
       <c r="N90">
-        <v>-1.721180800000001</v>
+        <v>-1.766762400000001</v>
       </c>
       <c r="O90">
-        <v>-0.4302952000000002</v>
+        <v>-0.4416906000000003</v>
       </c>
       <c r="P90">
-        <v>-1.290885600000001</v>
+        <v>-1.325071800000001</v>
       </c>
       <c r="Q90">
-        <v>1.039114399999999</v>
+        <v>1.004928199999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5520240624510929</v>
+        <v>0.5980444317648288</v>
       </c>
       <c r="T90">
-        <v>9.867249211523749</v>
+        <v>10.76427186711682</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1427260521390609</v>
+        <v>0.1411223886318804</v>
       </c>
       <c r="W90">
-        <v>0.1721406087304766</v>
+        <v>0.1724626243627184</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5709042085562435</v>
+        <v>0.5644895545275216</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2192766231769506</v>
+        <v>0.2208266231769505</v>
       </c>
       <c r="C91">
-        <v>-5.000825530691914</v>
+        <v>-5.316264485402252</v>
       </c>
       <c r="D91">
-        <v>14.86117446930809</v>
+        <v>14.77273551459775</v>
       </c>
       <c r="E91">
-        <v>7.303000000000003</v>
+        <v>7.530000000000003</v>
       </c>
       <c r="F91">
-        <v>20.203</v>
+        <v>20.43</v>
       </c>
       <c r="G91">
         <v>0.341</v>
@@ -8737,37 +8737,37 @@
         <v>2.29</v>
       </c>
       <c r="M91">
-        <v>4.056762400000001</v>
+        <v>4.102344</v>
       </c>
       <c r="N91">
-        <v>-1.766762400000001</v>
+        <v>-1.812344</v>
       </c>
       <c r="O91">
-        <v>-0.4416906000000003</v>
+        <v>-0.4530860000000001</v>
       </c>
       <c r="P91">
-        <v>-1.325071800000001</v>
+        <v>-1.359258</v>
       </c>
       <c r="Q91">
-        <v>1.004928199999999</v>
+        <v>0.9707419999999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5980444317648288</v>
+        <v>0.6532688749413117</v>
       </c>
       <c r="T91">
-        <v>10.76427186711682</v>
+        <v>11.8406990538285</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1411223886318804</v>
+        <v>0.1395543620915262</v>
       </c>
       <c r="W91">
-        <v>0.1724626243627184</v>
+        <v>0.1727774840920215</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5644895545275216</v>
+        <v>0.5582174483661049</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2208266231769505</v>
+        <v>0.2223766231769506</v>
       </c>
       <c r="C92">
-        <v>-5.316264485402252</v>
+        <v>-5.630657065401966</v>
       </c>
       <c r="D92">
-        <v>14.77273551459775</v>
+        <v>14.68534293459804</v>
       </c>
       <c r="E92">
-        <v>7.530000000000003</v>
+        <v>7.757000000000003</v>
       </c>
       <c r="F92">
-        <v>20.43</v>
+        <v>20.657</v>
       </c>
       <c r="G92">
         <v>0.341</v>
@@ -8819,37 +8819,37 @@
         <v>2.29</v>
       </c>
       <c r="M92">
-        <v>4.102344</v>
+        <v>4.147925600000001</v>
       </c>
       <c r="N92">
-        <v>-1.812344</v>
+        <v>-1.857925600000001</v>
       </c>
       <c r="O92">
-        <v>-0.4530860000000001</v>
+        <v>-0.4644814000000002</v>
       </c>
       <c r="P92">
-        <v>-1.359258</v>
+        <v>-1.3934442</v>
       </c>
       <c r="Q92">
-        <v>0.9707419999999998</v>
+        <v>0.9365557999999996</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6532688749413117</v>
+        <v>0.7207654166014574</v>
       </c>
       <c r="T92">
-        <v>11.8406990538285</v>
+        <v>13.15633228203167</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1395543620915262</v>
+        <v>0.138020797672938</v>
       </c>
       <c r="W92">
-        <v>0.1727774840920215</v>
+        <v>0.1730854238272741</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5582174483661049</v>
+        <v>0.5520831906917519</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2223766231769506</v>
+        <v>0.2239266231769506</v>
       </c>
       <c r="C93">
-        <v>-5.630657065401966</v>
+        <v>-5.944021731915285</v>
       </c>
       <c r="D93">
-        <v>14.68534293459804</v>
+        <v>14.59897826808472</v>
       </c>
       <c r="E93">
-        <v>7.757000000000003</v>
+        <v>7.984000000000004</v>
       </c>
       <c r="F93">
-        <v>20.657</v>
+        <v>20.884</v>
       </c>
       <c r="G93">
         <v>0.341</v>
@@ -8901,37 +8901,37 @@
         <v>2.29</v>
       </c>
       <c r="M93">
-        <v>4.147925600000001</v>
+        <v>4.193507200000001</v>
       </c>
       <c r="N93">
-        <v>-1.857925600000001</v>
+        <v>-1.903507200000001</v>
       </c>
       <c r="O93">
-        <v>-0.4644814000000002</v>
+        <v>-0.4758768000000002</v>
       </c>
       <c r="P93">
-        <v>-1.3934442</v>
+        <v>-1.427630400000001</v>
       </c>
       <c r="Q93">
-        <v>0.9365557999999996</v>
+        <v>0.9023695999999994</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7207654166014574</v>
+        <v>0.80513609367664</v>
       </c>
       <c r="T93">
-        <v>13.15633228203167</v>
+        <v>14.80087381728563</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.138020797672938</v>
+        <v>0.1365205716112756</v>
       </c>
       <c r="W93">
-        <v>0.1730854238272741</v>
+        <v>0.1733866692204559</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5520831906917519</v>
+        <v>0.5460822864451025</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2239266231769506</v>
+        <v>0.2254766231769506</v>
       </c>
       <c r="C94">
-        <v>-5.944021731915285</v>
+        <v>-6.256376514422859</v>
       </c>
       <c r="D94">
-        <v>14.59897826808472</v>
+        <v>14.51362348557715</v>
       </c>
       <c r="E94">
-        <v>7.984000000000004</v>
+        <v>8.211000000000004</v>
       </c>
       <c r="F94">
-        <v>20.884</v>
+        <v>21.111</v>
       </c>
       <c r="G94">
         <v>0.341</v>
@@ -8983,37 +8983,37 @@
         <v>2.29</v>
       </c>
       <c r="M94">
-        <v>4.193507200000001</v>
+        <v>4.239088800000001</v>
       </c>
       <c r="N94">
-        <v>-1.903507200000001</v>
+        <v>-1.949088800000001</v>
       </c>
       <c r="O94">
-        <v>-0.4758768000000002</v>
+        <v>-0.4872722000000003</v>
       </c>
       <c r="P94">
-        <v>-1.427630400000001</v>
+        <v>-1.461816600000001</v>
       </c>
       <c r="Q94">
-        <v>0.9023695999999994</v>
+        <v>0.8681833999999993</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.80513609367664</v>
+        <v>0.9136126784875888</v>
       </c>
       <c r="T94">
-        <v>14.80087381728563</v>
+        <v>16.91528436261216</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1365205716112756</v>
+        <v>0.1350526084756705</v>
       </c>
       <c r="W94">
-        <v>0.1733866692204559</v>
+        <v>0.1736814362180854</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5460822864451025</v>
+        <v>0.540210433902682</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2254766231769506</v>
+        <v>0.2270266231769505</v>
       </c>
       <c r="C95">
-        <v>-6.256376514422859</v>
+        <v>-6.567739023209613</v>
       </c>
       <c r="D95">
-        <v>14.51362348557715</v>
+        <v>14.42926097679039</v>
       </c>
       <c r="E95">
-        <v>8.211000000000004</v>
+        <v>8.438000000000004</v>
       </c>
       <c r="F95">
-        <v>21.111</v>
+        <v>21.338</v>
       </c>
       <c r="G95">
         <v>0.341</v>
@@ -9065,37 +9065,37 @@
         <v>2.29</v>
       </c>
       <c r="M95">
-        <v>4.239088800000001</v>
+        <v>4.284670400000001</v>
       </c>
       <c r="N95">
-        <v>-1.949088800000001</v>
+        <v>-1.994670400000001</v>
       </c>
       <c r="O95">
-        <v>-0.4872722000000003</v>
+        <v>-0.4986676000000003</v>
       </c>
       <c r="P95">
-        <v>-1.461816600000001</v>
+        <v>-1.496002800000001</v>
       </c>
       <c r="Q95">
-        <v>0.8681833999999993</v>
+        <v>0.8339971999999991</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9136126784875888</v>
+        <v>1.058248124902187</v>
       </c>
       <c r="T95">
-        <v>16.91528436261216</v>
+        <v>19.73449842304752</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1350526084756705</v>
+        <v>0.1336158785982697</v>
       </c>
       <c r="W95">
-        <v>0.1736814362180854</v>
+        <v>0.1739699315774674</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.540210433902682</v>
+        <v>0.5344635143930789</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2270266231769505</v>
+        <v>0.2285766231769506</v>
       </c>
       <c r="C96">
-        <v>-6.567739023209613</v>
+        <v>-6.878126461477528</v>
       </c>
       <c r="D96">
-        <v>14.42926097679039</v>
+        <v>14.34587353852248</v>
       </c>
       <c r="E96">
-        <v>8.438000000000004</v>
+        <v>8.665000000000004</v>
       </c>
       <c r="F96">
-        <v>21.338</v>
+        <v>21.565</v>
       </c>
       <c r="G96">
         <v>0.341</v>
@@ -9147,37 +9147,37 @@
         <v>2.29</v>
       </c>
       <c r="M96">
-        <v>4.284670400000001</v>
+        <v>4.330252000000002</v>
       </c>
       <c r="N96">
-        <v>-1.994670400000001</v>
+        <v>-2.040252000000002</v>
       </c>
       <c r="O96">
-        <v>-0.4986676000000003</v>
+        <v>-0.5100630000000004</v>
       </c>
       <c r="P96">
-        <v>-1.496002800000001</v>
+        <v>-1.530189000000001</v>
       </c>
       <c r="Q96">
-        <v>0.8339971999999991</v>
+        <v>0.7998109999999989</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.058248124902187</v>
+        <v>1.260737749882625</v>
       </c>
       <c r="T96">
-        <v>19.73449842304752</v>
+        <v>23.68139810765703</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1336158785982697</v>
+        <v>0.1322093956656564</v>
       </c>
       <c r="W96">
-        <v>0.1739699315774674</v>
+        <v>0.1742523533503362</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5344635143930789</v>
+        <v>0.5288375826626255</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2285766231769506</v>
+        <v>0.2301266231769506</v>
       </c>
       <c r="C97">
-        <v>-6.878126461477528</v>
+        <v>-7.187555637040795</v>
       </c>
       <c r="D97">
-        <v>14.34587353852248</v>
+        <v>14.26344436295921</v>
       </c>
       <c r="E97">
-        <v>8.665000000000004</v>
+        <v>8.892000000000005</v>
       </c>
       <c r="F97">
-        <v>21.565</v>
+        <v>21.79200000000001</v>
       </c>
       <c r="G97">
         <v>0.341</v>
@@ -9229,37 +9229,37 @@
         <v>2.29</v>
       </c>
       <c r="M97">
-        <v>4.330252000000002</v>
+        <v>4.375833600000001</v>
       </c>
       <c r="N97">
-        <v>-2.040252000000002</v>
+        <v>-2.085833600000001</v>
       </c>
       <c r="O97">
-        <v>-0.5100630000000004</v>
+        <v>-0.5214584000000002</v>
       </c>
       <c r="P97">
-        <v>-1.530189000000001</v>
+        <v>-1.564375200000001</v>
       </c>
       <c r="Q97">
-        <v>0.7998109999999989</v>
+        <v>0.7656247999999994</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.260737749882625</v>
+        <v>1.564472187353282</v>
       </c>
       <c r="T97">
-        <v>23.68139810765703</v>
+        <v>29.6017476345713</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1322093956656564</v>
+        <v>0.1308322144608058</v>
       </c>
       <c r="W97">
-        <v>0.1742523533503362</v>
+        <v>0.1745288913362702</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5288375826626255</v>
+        <v>0.5233288578432231</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2301266231769505</v>
+        <v>0.2316766231769505</v>
       </c>
       <c r="C98">
-        <v>-7.18755563704079</v>
+        <v>-7.496042973620126</v>
       </c>
       <c r="D98">
-        <v>14.26344436295921</v>
+        <v>14.18195702637988</v>
       </c>
       <c r="E98">
-        <v>8.892000000000001</v>
+        <v>9.119000000000002</v>
       </c>
       <c r="F98">
-        <v>21.792</v>
+        <v>22.019</v>
       </c>
       <c r="G98">
         <v>0.341</v>
@@ -9311,37 +9311,37 @@
         <v>2.29</v>
       </c>
       <c r="M98">
-        <v>4.375833600000001</v>
+        <v>4.4214152</v>
       </c>
       <c r="N98">
-        <v>-2.085833600000001</v>
+        <v>-2.1314152</v>
       </c>
       <c r="O98">
-        <v>-0.5214584000000002</v>
+        <v>-0.5328538</v>
       </c>
       <c r="P98">
-        <v>-1.564375200000001</v>
+        <v>-1.5985614</v>
       </c>
       <c r="Q98">
-        <v>0.7656247999999994</v>
+        <v>0.7314385999999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.564472187353278</v>
+        <v>2.07069624980437</v>
       </c>
       <c r="T98">
-        <v>29.60174763457122</v>
+        <v>39.46899684609496</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1308322144608058</v>
+        <v>0.129483428744715</v>
       </c>
       <c r="W98">
-        <v>0.1745288913362702</v>
+        <v>0.1747997275080612</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5233288578432231</v>
+        <v>0.5179337149788601</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2316766231769505</v>
+        <v>0.2332266231769505</v>
       </c>
       <c r="C99">
-        <v>-7.496042973620126</v>
+        <v>-7.803604521752105</v>
       </c>
       <c r="D99">
-        <v>14.18195702637988</v>
+        <v>14.1013954782479</v>
       </c>
       <c r="E99">
-        <v>9.119000000000002</v>
+        <v>9.346000000000002</v>
       </c>
       <c r="F99">
-        <v>22.019</v>
+        <v>22.246</v>
       </c>
       <c r="G99">
         <v>0.341</v>
@@ -9393,37 +9393,37 @@
         <v>2.29</v>
       </c>
       <c r="M99">
-        <v>4.4214152</v>
+        <v>4.4669968</v>
       </c>
       <c r="N99">
-        <v>-2.1314152</v>
+        <v>-2.1769968</v>
       </c>
       <c r="O99">
-        <v>-0.5328538</v>
+        <v>-0.5442492000000001</v>
       </c>
       <c r="P99">
-        <v>-1.5985614</v>
+        <v>-1.6327476</v>
       </c>
       <c r="Q99">
-        <v>0.7314385999999999</v>
+        <v>0.6972523999999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.07069624980437</v>
+        <v>3.083144374706555</v>
       </c>
       <c r="T99">
-        <v>39.46899684609496</v>
+        <v>59.20349526914244</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.129483428744715</v>
+        <v>0.1281621692677281</v>
       </c>
       <c r="W99">
-        <v>0.1747997275080612</v>
+        <v>0.1750650364110402</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5179337149788601</v>
+        <v>0.5126486770709126</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2332266231769505</v>
+        <v>0.2347766231769506</v>
       </c>
       <c r="C100">
-        <v>-7.803604521752105</v>
+        <v>-8.110255969328771</v>
       </c>
       <c r="D100">
-        <v>14.1013954782479</v>
+        <v>14.02174403067123</v>
       </c>
       <c r="E100">
-        <v>9.346000000000002</v>
+        <v>9.573000000000002</v>
       </c>
       <c r="F100">
-        <v>22.246</v>
+        <v>22.473</v>
       </c>
       <c r="G100">
         <v>0.341</v>
@@ -9475,37 +9475,37 @@
         <v>2.29</v>
       </c>
       <c r="M100">
-        <v>4.4669968</v>
+        <v>4.512578400000001</v>
       </c>
       <c r="N100">
-        <v>-2.1769968</v>
+        <v>-2.222578400000001</v>
       </c>
       <c r="O100">
-        <v>-0.5442492000000001</v>
+        <v>-0.5556446000000002</v>
       </c>
       <c r="P100">
-        <v>-1.6327476</v>
+        <v>-1.6669338</v>
       </c>
       <c r="Q100">
-        <v>0.6972523999999998</v>
+        <v>0.6630661999999996</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.083144374706555</v>
+        <v>6.120488749413111</v>
       </c>
       <c r="T100">
-        <v>59.20349526914244</v>
+        <v>118.4069905382849</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1281621692677281</v>
+        <v>0.1268676019013875</v>
       </c>
       <c r="W100">
-        <v>0.1750650364110402</v>
+        <v>0.1753249855382014</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5126486770709126</v>
+        <v>0.5074704076055498</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2347766231769506</v>
-      </c>
-      <c r="C101">
-        <v>-8.110255969328771</v>
-      </c>
-      <c r="D101">
-        <v>14.02174403067123</v>
-      </c>
-      <c r="E101">
-        <v>9.573000000000002</v>
-      </c>
-      <c r="F101">
-        <v>22.473</v>
-      </c>
-      <c r="G101">
-        <v>0.341</v>
-      </c>
-      <c r="H101">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.62</v>
-      </c>
-      <c r="K101">
-        <v>2.33</v>
-      </c>
-      <c r="L101">
-        <v>2.29</v>
-      </c>
-      <c r="M101">
-        <v>4.512578400000001</v>
-      </c>
-      <c r="N101">
-        <v>-2.222578400000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.5556446000000002</v>
-      </c>
-      <c r="P101">
-        <v>-1.6669338</v>
-      </c>
-      <c r="Q101">
-        <v>0.6630661999999996</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.120488749413111</v>
-      </c>
-      <c r="T101">
-        <v>118.4069905382849</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1268676019013875</v>
-      </c>
-      <c r="W101">
-        <v>0.1753249855382014</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5074704076055498</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
